--- a/works/repair-ledger/repair-ledger-sample.xlsx
+++ b/works/repair-ledger/repair-ledger-sample.xlsx
@@ -12,13 +12,11 @@
     <sheet name="工单台账" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="仪表盘" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="单元查询" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="入户维修评价表" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="设置" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">仪表盘!$A$1:$N$93</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">使用说明!$A$1:$D$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">入户维修评价表!$A$1:$F$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">使用说明!$A$1:$D$35</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">单元查询!$A$1:$M$29</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">工单台账!$6:$6</definedName>
     <definedName function="false" hidden="false" name="可派单" vbProcedure="false">设置!$B$9:$B$14</definedName>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="571">
   <si>
     <t xml:space="preserve">工程维修台账 · 使用说明</t>
   </si>
@@ -78,9 +76,6 @@
     <t xml:space="preserve">⑤ 评价与回访</t>
   </si>
   <si>
-    <t xml:space="preserve">评价表收回后录入「维修评价」「业主意见与建议」。仪表盘第一部分列出未结和重复报修的住户，用来排回访。</t>
-  </si>
-  <si>
     <t xml:space="preserve">二、各表分工</t>
   </si>
   <si>
@@ -102,12 +97,6 @@
     <t xml:space="preserve">选楼栋、填房号，列出这一户的全部维修记录。接业主电话时用。</t>
   </si>
   <si>
-    <t xml:space="preserve">入户维修评价表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上门时打印，业主验收签字。栏目和台账对应，回来按单据编号录入。</t>
-  </si>
-  <si>
     <t xml:space="preserve">设置</t>
   </si>
   <si>
@@ -921,101 +910,6 @@
     <t xml:space="preserve">第几单</t>
   </si>
   <si>
-    <t xml:space="preserve">建发央玺超一级物业服务 · 入户维修评价表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">单据编号：______________________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">说明：本表用于记录建发央玺超一级物业服务的免费入户维修（耗材费用另计），请业主验收后签字。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">楼栋房号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　栋　　　　　　室</t>
-  </si>
-  <si>
-    <t xml:space="preserve">业主姓名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">联系电话</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修日期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　年　　月　　日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修人员</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上门时间</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一、维修内容登记</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修部位及问题描述：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修类别：□ 门窗五金　□ 电气照明　□ 给排水　□ 空调暖通　□ 渗漏防水
-　　　　　□ 墙地饰面　□ 燃气厨电　□ 弱电门禁　□ 其他 __________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修整改结果：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">□ 问题已完全修复　　□ 部分整改，需二次上门　　□ 暂无法处理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">完工时间：____月____日 ____时____分　　□ 需二次上门，预约 ____月____日 ____时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">耗材使用：□ 无需耗材　□ 业主自备　□ 物业代购，金额 ________ 元
-耗材明细：______________________________________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">二、业主满意度及验收评价</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本次入户维修整体评价：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">□ 非常满意　　□ 满意　　□ 一般　　□ 不满意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">业主意见与建议：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三、签字确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">业主签字：__________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日期：______年______月______日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">维修人员签字：__________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物业经理：__________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">四、回访记录（客服中心填写）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回访日期：____年___月___日　　回访人：__________　　方式：□ 电话　□ 上门　□ 微信</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回访结果：□ 已解决，业主满意　□ 问题复发，需返修　□ 其他：______________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">备注：业主签字确认即视为本次上门维修项目已现场验收完毕，本单据由物业工程部存档。</t>
-  </si>
-  <si>
     <t xml:space="preserve">米黄色格可以改；灰字区域是公式，别动。改了名单，台账的下拉和仪表盘会一起变。</t>
   </si>
   <si>
@@ -1854,6 +1748,9 @@
   </si>
   <si>
     <t xml:space="preserve">示例固定在 2025-05-07，日常使用请清空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完工后请业主评价，录入「维修评价」「业主意见与建议」。仪表盘第一部分列出未结和重复报修的住户，用来排回访。</t>
   </si>
 </sst>
 </file>
@@ -4284,7 +4181,7 @@
     <tabColor rgb="FFB0AEA5"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B2:C34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -4348,171 +4245,163 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="65.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="5" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
+    <row r="20" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="5" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="5" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="5" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="5" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="5" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4520,9 +4409,9 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4564,7 +4453,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4572,7 +4461,7 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
       <c r="G1" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
@@ -4589,14 +4478,14 @@
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="15" t="str">
@@ -4620,7 +4509,7 @@
         <v>刘师傅</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
@@ -4636,26 +4525,26 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
       <c r="F3" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N3" s="16"/>
       <c r="O3" s="16"/>
@@ -4663,14 +4552,14 @@
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="19" t="str">
@@ -4694,7 +4583,7 @@
         <v>在岗 3 单</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
@@ -4703,61 +4592,61 @@
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="E6" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="F6" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="G6" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="H6" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="J6" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="K6" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="L6" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="M6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="N6" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="O6" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="P6" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="Q6" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="R6" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="21" t="s">
+      <c r="S6" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="Q6" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4769,34 +4658,34 @@
         <v>45778</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="H7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="I7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="G7" s="19" t="s">
+      <c r="J7" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="L7" s="19" t="s">
         <v>86</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>89</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="25" t="str">
@@ -4808,11 +4697,11 @@
         <v>1</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>346</v>
+        <v>312</v>
       </c>
       <c r="Q7" s="27"/>
       <c r="R7" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S7" s="24"/>
     </row>
@@ -4825,32 +4714,32 @@
         <v>45778</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H8" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M8" s="23"/>
       <c r="N8" s="25" t="n">
@@ -4862,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="Q8" s="27"/>
       <c r="R8" s="19"/>
@@ -4877,30 +4766,30 @@
         <v>45778</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="25" t="str">
@@ -4912,11 +4801,11 @@
         <v>1</v>
       </c>
       <c r="P9" s="24" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="Q9" s="27"/>
       <c r="R9" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S9" s="24"/>
     </row>
@@ -4929,30 +4818,30 @@
         <v>45778</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="25" t="str">
@@ -4964,11 +4853,11 @@
         <v>1</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="Q10" s="27"/>
       <c r="R10" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S10" s="24"/>
     </row>
@@ -4981,30 +4870,30 @@
         <v>45778</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H11" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="19" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="25" t="str">
@@ -5016,11 +4905,11 @@
         <v>1</v>
       </c>
       <c r="P11" s="24" t="s">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="Q11" s="27"/>
       <c r="R11" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S11" s="24"/>
     </row>
@@ -5033,30 +4922,30 @@
         <v>45778</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I12" s="19"/>
       <c r="J12" s="19" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="25" t="str">
@@ -5068,14 +4957,14 @@
         <v>1</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="Q12" s="27"/>
       <c r="R12" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5087,32 +4976,32 @@
         <v>45778</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="25" t="n">
@@ -5124,14 +5013,14 @@
         <v>1</v>
       </c>
       <c r="P13" s="24" t="s">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="Q13" s="27"/>
       <c r="R13" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,30 +5032,30 @@
         <v>45778</v>
       </c>
       <c r="C14" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="G14" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>85</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M14" s="23"/>
       <c r="N14" s="25" t="n">
@@ -5178,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="24" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="Q14" s="27"/>
       <c r="R14" s="19"/>
@@ -5193,30 +5082,30 @@
         <v>45778</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="19" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="25" t="str">
@@ -5228,11 +5117,11 @@
         <v>1</v>
       </c>
       <c r="P15" s="24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q15" s="27"/>
       <c r="R15" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S15" s="24"/>
     </row>
@@ -5245,32 +5134,32 @@
         <v>45778</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I16" s="19"/>
       <c r="J16" s="19" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="25" t="str">
@@ -5284,10 +5173,10 @@
       <c r="P16" s="24"/>
       <c r="Q16" s="27"/>
       <c r="R16" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5299,32 +5188,32 @@
         <v>45778</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="19" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="25" t="str">
@@ -5336,11 +5225,11 @@
         <v>1</v>
       </c>
       <c r="P17" s="24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q17" s="27"/>
       <c r="R17" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S17" s="24"/>
     </row>
@@ -5353,32 +5242,32 @@
         <v>45778</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H18" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I18" s="19"/>
       <c r="J18" s="19" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="25" t="str">
@@ -5390,14 +5279,14 @@
         <v>1</v>
       </c>
       <c r="P18" s="24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q18" s="27"/>
       <c r="R18" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5409,32 +5298,32 @@
         <v>45778</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="19" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L19" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="25" t="str">
@@ -5446,11 +5335,11 @@
         <v>1</v>
       </c>
       <c r="P19" s="24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q19" s="27"/>
       <c r="R19" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S19" s="24"/>
     </row>
@@ -5463,30 +5352,30 @@
         <v>45778</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I20" s="19"/>
       <c r="J20" s="19" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="25" t="str">
@@ -5500,7 +5389,7 @@
       <c r="P20" s="24"/>
       <c r="Q20" s="27"/>
       <c r="R20" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S20" s="24"/>
     </row>
@@ -5513,30 +5402,30 @@
         <v>45778</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="G21" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>380</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H21" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I21" s="19"/>
       <c r="J21" s="19" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="K21" s="19"/>
       <c r="L21" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="25" t="str">
@@ -5548,11 +5437,11 @@
         <v>1</v>
       </c>
       <c r="P21" s="24" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="Q21" s="27"/>
       <c r="R21" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S21" s="24"/>
     </row>
@@ -5565,32 +5454,32 @@
         <v>45778</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I22" s="19"/>
       <c r="J22" s="19" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="25" t="str">
@@ -5602,11 +5491,11 @@
         <v>1</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="Q22" s="27"/>
       <c r="R22" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S22" s="24"/>
     </row>
@@ -5619,30 +5508,30 @@
         <v>45778</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I23" s="19"/>
       <c r="J23" s="19" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="25" t="str">
@@ -5656,10 +5545,10 @@
       <c r="P23" s="24"/>
       <c r="Q23" s="27"/>
       <c r="R23" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S23" s="24" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5671,30 +5560,30 @@
         <v>45778</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="19" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="25" t="str">
@@ -5708,7 +5597,7 @@
       <c r="P24" s="24"/>
       <c r="Q24" s="27"/>
       <c r="R24" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S24" s="24"/>
     </row>
@@ -5721,30 +5610,30 @@
         <v>45778</v>
       </c>
       <c r="C25" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="G25" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H25" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I25" s="19"/>
       <c r="J25" s="19" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="K25" s="19"/>
       <c r="L25" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="25" t="str">
@@ -5758,7 +5647,7 @@
       <c r="P25" s="24"/>
       <c r="Q25" s="27"/>
       <c r="R25" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S25" s="24"/>
     </row>
@@ -5771,32 +5660,32 @@
         <v>45778</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="19" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="25" t="str">
@@ -5810,7 +5699,7 @@
       <c r="P26" s="24"/>
       <c r="Q26" s="27"/>
       <c r="R26" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S26" s="24"/>
     </row>
@@ -5823,30 +5712,30 @@
         <v>45778</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="K27" s="19"/>
       <c r="L27" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="25" t="str">
@@ -5858,11 +5747,11 @@
         <v>1</v>
       </c>
       <c r="P27" s="24" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="Q27" s="27"/>
       <c r="R27" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S27" s="24"/>
     </row>
@@ -5875,30 +5764,30 @@
         <v>45778</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="19" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="25" t="str">
@@ -5912,10 +5801,10 @@
       <c r="P28" s="24"/>
       <c r="Q28" s="27"/>
       <c r="R28" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S28" s="24" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5927,32 +5816,32 @@
         <v>45778</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F29" s="24" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="25" t="str">
@@ -5966,7 +5855,7 @@
       <c r="P29" s="24"/>
       <c r="Q29" s="27"/>
       <c r="R29" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S29" s="24"/>
     </row>
@@ -5979,30 +5868,30 @@
         <v>45778</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="19" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="25" t="str">
@@ -6014,11 +5903,11 @@
         <v>1</v>
       </c>
       <c r="P30" s="24" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q30" s="27"/>
       <c r="R30" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S30" s="24"/>
     </row>
@@ -6031,30 +5920,30 @@
         <v>45778</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I31" s="19"/>
       <c r="J31" s="19" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="K31" s="19"/>
       <c r="L31" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="25" t="str">
@@ -6079,32 +5968,32 @@
         <v>45778</v>
       </c>
       <c r="C32" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="F32" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="I32" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="F32" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>144</v>
-      </c>
       <c r="J32" s="19" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="25" t="str">
@@ -6129,32 +6018,32 @@
         <v>45778</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D33" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>143</v>
-      </c>
       <c r="I33" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="K33" s="19"/>
       <c r="L33" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="25" t="str">
@@ -6179,30 +6068,30 @@
         <v>45778</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="K34" s="19"/>
       <c r="L34" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="25" t="str">
@@ -6227,28 +6116,28 @@
         <v>45778</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
       <c r="L35" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="25" t="n">
@@ -6260,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="24" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q35" s="27"/>
       <c r="R35" s="19"/>
@@ -6275,30 +6164,30 @@
         <v>45778</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I36" s="19"/>
       <c r="J36" s="19" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="25" t="str">
@@ -6323,30 +6212,30 @@
         <v>45778</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I37" s="19"/>
       <c r="J37" s="19" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="25" t="str">
@@ -6358,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="24" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="Q37" s="27"/>
       <c r="R37" s="19"/>
@@ -6373,32 +6262,32 @@
         <v>45778</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="25" t="str">
@@ -6423,30 +6312,30 @@
         <v>45778</v>
       </c>
       <c r="C39" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>141</v>
-      </c>
       <c r="F39" s="24" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I39" s="19"/>
       <c r="J39" s="19" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="K39" s="19"/>
       <c r="L39" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="25" t="n">
@@ -6458,7 +6347,7 @@
         <v>2</v>
       </c>
       <c r="P39" s="24" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="Q39" s="27"/>
       <c r="R39" s="19"/>
@@ -6473,30 +6362,30 @@
         <v>45778</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="K40" s="19"/>
       <c r="L40" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="25" t="str">
@@ -6521,32 +6410,32 @@
         <v>45778</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="K41" s="19"/>
       <c r="L41" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="25" t="n">
@@ -6558,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="24" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="Q41" s="27"/>
       <c r="R41" s="19"/>
@@ -6573,30 +6462,30 @@
         <v>45779</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I42" s="19"/>
       <c r="J42" s="19" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M42" s="23"/>
       <c r="N42" s="25" t="n">
@@ -6608,11 +6497,11 @@
         <v>1</v>
       </c>
       <c r="P42" s="24" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="Q42" s="27"/>
       <c r="R42" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S42" s="24"/>
     </row>
@@ -6625,30 +6514,30 @@
         <v>45779</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I43" s="19"/>
       <c r="J43" s="19" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K43" s="19"/>
       <c r="L43" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M43" s="23"/>
       <c r="N43" s="25" t="str">
@@ -6660,11 +6549,11 @@
         <v>1</v>
       </c>
       <c r="P43" s="24" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="Q43" s="27"/>
       <c r="R43" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S43" s="24"/>
     </row>
@@ -6677,30 +6566,30 @@
         <v>45779</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="K44" s="19"/>
       <c r="L44" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M44" s="23"/>
       <c r="N44" s="25" t="str">
@@ -6714,7 +6603,7 @@
       <c r="P44" s="24"/>
       <c r="Q44" s="27"/>
       <c r="R44" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S44" s="24"/>
     </row>
@@ -6727,32 +6616,32 @@
         <v>45779</v>
       </c>
       <c r="C45" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="G45" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>427</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H45" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="19" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="K45" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L45" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M45" s="23"/>
       <c r="N45" s="25" t="str">
@@ -6764,11 +6653,11 @@
         <v>1</v>
       </c>
       <c r="P45" s="24" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q45" s="27"/>
       <c r="R45" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S45" s="24"/>
     </row>
@@ -6781,30 +6670,30 @@
         <v>45779</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I46" s="19"/>
       <c r="J46" s="19" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K46" s="19"/>
       <c r="L46" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M46" s="23"/>
       <c r="N46" s="25" t="str">
@@ -6818,7 +6707,7 @@
       <c r="P46" s="24"/>
       <c r="Q46" s="27"/>
       <c r="R46" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S46" s="24"/>
     </row>
@@ -6831,30 +6720,30 @@
         <v>45779</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I47" s="19"/>
       <c r="J47" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K47" s="19"/>
       <c r="L47" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M47" s="23"/>
       <c r="N47" s="25" t="str">
@@ -6868,7 +6757,7 @@
       <c r="P47" s="24"/>
       <c r="Q47" s="27"/>
       <c r="R47" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S47" s="24"/>
     </row>
@@ -6881,32 +6770,32 @@
         <v>45779</v>
       </c>
       <c r="C48" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="G48" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D48" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H48" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I48" s="19"/>
       <c r="J48" s="19" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M48" s="23"/>
       <c r="N48" s="25" t="n">
@@ -6918,11 +6807,11 @@
         <v>1</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="Q48" s="27"/>
       <c r="R48" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S48" s="24"/>
     </row>
@@ -6935,32 +6824,32 @@
         <v>45779</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I49" s="19"/>
       <c r="J49" s="19" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L49" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M49" s="23"/>
       <c r="N49" s="25" t="str">
@@ -6974,7 +6863,7 @@
       <c r="P49" s="24"/>
       <c r="Q49" s="27"/>
       <c r="R49" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S49" s="24"/>
     </row>
@@ -6987,32 +6876,32 @@
         <v>45779</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I50" s="19"/>
       <c r="J50" s="19" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L50" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M50" s="23"/>
       <c r="N50" s="25" t="str">
@@ -7026,10 +6915,10 @@
       <c r="P50" s="24"/>
       <c r="Q50" s="27"/>
       <c r="R50" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S50" s="24" t="s">
-        <v>437</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7041,32 +6930,32 @@
         <v>45779</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I51" s="19"/>
       <c r="J51" s="19" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M51" s="23"/>
       <c r="N51" s="25" t="n">
@@ -7078,11 +6967,11 @@
         <v>1</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="Q51" s="27"/>
       <c r="R51" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S51" s="24"/>
     </row>
@@ -7095,32 +6984,32 @@
         <v>45779</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I52" s="19"/>
       <c r="J52" s="19" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M52" s="23"/>
       <c r="N52" s="25" t="str">
@@ -7134,7 +7023,7 @@
       <c r="P52" s="24"/>
       <c r="Q52" s="27"/>
       <c r="R52" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S52" s="24"/>
     </row>
@@ -7147,32 +7036,32 @@
         <v>45779</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F53" s="24" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I53" s="19"/>
       <c r="J53" s="19" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M53" s="23"/>
       <c r="N53" s="25" t="str">
@@ -7184,11 +7073,11 @@
         <v>1</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="Q53" s="27"/>
       <c r="R53" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S53" s="24"/>
     </row>
@@ -7201,30 +7090,30 @@
         <v>45779</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F54" s="24" t="s">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I54" s="19"/>
       <c r="J54" s="19" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="K54" s="19"/>
       <c r="L54" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M54" s="23"/>
       <c r="N54" s="25" t="str">
@@ -7236,11 +7125,11 @@
         <v>1</v>
       </c>
       <c r="P54" s="24" t="s">
-        <v>447</v>
+        <v>413</v>
       </c>
       <c r="Q54" s="27"/>
       <c r="R54" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S54" s="24"/>
     </row>
@@ -7253,30 +7142,30 @@
         <v>45779</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I55" s="19"/>
       <c r="J55" s="19" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M55" s="23"/>
       <c r="N55" s="25" t="str">
@@ -7290,7 +7179,7 @@
       <c r="P55" s="24"/>
       <c r="Q55" s="27"/>
       <c r="R55" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S55" s="24"/>
     </row>
@@ -7303,30 +7192,30 @@
         <v>45779</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F56" s="24" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I56" s="19"/>
       <c r="J56" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K56" s="19"/>
       <c r="L56" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M56" s="23"/>
       <c r="N56" s="25" t="str">
@@ -7338,11 +7227,11 @@
         <v>1</v>
       </c>
       <c r="P56" s="24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q56" s="27"/>
       <c r="R56" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S56" s="24"/>
     </row>
@@ -7355,32 +7244,32 @@
         <v>45779</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I57" s="19"/>
       <c r="J57" s="19" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="K57" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M57" s="23"/>
       <c r="N57" s="25" t="str">
@@ -7394,7 +7283,7 @@
       <c r="P57" s="24"/>
       <c r="Q57" s="27"/>
       <c r="R57" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S57" s="24"/>
     </row>
@@ -7407,30 +7296,30 @@
         <v>45779</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I58" s="19"/>
       <c r="J58" s="19" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="K58" s="19"/>
       <c r="L58" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M58" s="23"/>
       <c r="N58" s="25" t="str">
@@ -7444,7 +7333,7 @@
       <c r="P58" s="24"/>
       <c r="Q58" s="27"/>
       <c r="R58" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S58" s="24"/>
     </row>
@@ -7457,32 +7346,32 @@
         <v>45779</v>
       </c>
       <c r="C59" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="G59" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="H59" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F59" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>86</v>
-      </c>
       <c r="I59" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J59" s="19" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
       <c r="K59" s="19"/>
       <c r="L59" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M59" s="23"/>
       <c r="N59" s="25" t="str">
@@ -7494,11 +7383,11 @@
         <v>1</v>
       </c>
       <c r="P59" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q59" s="27"/>
       <c r="R59" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S59" s="24"/>
     </row>
@@ -7511,30 +7400,30 @@
         <v>45779</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I60" s="19"/>
       <c r="J60" s="19" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="K60" s="19"/>
       <c r="L60" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M60" s="23"/>
       <c r="N60" s="25" t="str">
@@ -7548,7 +7437,7 @@
       <c r="P60" s="24"/>
       <c r="Q60" s="27"/>
       <c r="R60" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S60" s="24"/>
     </row>
@@ -7561,32 +7450,32 @@
         <v>45779</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F61" s="24" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I61" s="19"/>
       <c r="J61" s="19" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L61" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M61" s="23"/>
       <c r="N61" s="25" t="n">
@@ -7598,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="P61" s="24" t="s">
-        <v>459</v>
+        <v>425</v>
       </c>
       <c r="Q61" s="27"/>
       <c r="R61" s="19"/>
@@ -7613,30 +7502,30 @@
         <v>45779</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I62" s="19"/>
       <c r="J62" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K62" s="19"/>
       <c r="L62" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M62" s="23"/>
       <c r="N62" s="25" t="str">
@@ -7661,30 +7550,30 @@
         <v>45779</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I63" s="19"/>
       <c r="J63" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K63" s="19"/>
       <c r="L63" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M63" s="23"/>
       <c r="N63" s="25" t="str">
@@ -7709,30 +7598,30 @@
         <v>45779</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I64" s="19"/>
       <c r="J64" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K64" s="19"/>
       <c r="L64" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M64" s="23"/>
       <c r="N64" s="25" t="str">
@@ -7744,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q64" s="27"/>
       <c r="R64" s="19"/>
@@ -7759,30 +7648,30 @@
         <v>45779</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F65" s="24" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I65" s="19"/>
       <c r="J65" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K65" s="19"/>
       <c r="L65" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M65" s="23"/>
       <c r="N65" s="25" t="str">
@@ -7807,30 +7696,30 @@
         <v>45779</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I66" s="19"/>
       <c r="J66" s="19" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="K66" s="19"/>
       <c r="L66" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M66" s="23"/>
       <c r="N66" s="25" t="str">
@@ -7855,30 +7744,30 @@
         <v>45780</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I67" s="19"/>
       <c r="J67" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K67" s="19"/>
       <c r="L67" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M67" s="23"/>
       <c r="N67" s="25" t="str">
@@ -7892,7 +7781,7 @@
       <c r="P67" s="24"/>
       <c r="Q67" s="27"/>
       <c r="R67" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S67" s="24"/>
     </row>
@@ -7905,30 +7794,30 @@
         <v>45780</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I68" s="19"/>
       <c r="J68" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K68" s="19"/>
       <c r="L68" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M68" s="23"/>
       <c r="N68" s="25" t="str">
@@ -7942,10 +7831,10 @@
       <c r="P68" s="24"/>
       <c r="Q68" s="27"/>
       <c r="R68" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S68" s="24" t="s">
-        <v>469</v>
+        <v>435</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7957,30 +7846,30 @@
         <v>45780</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D69" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="G69" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E69" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>470</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="H69" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I69" s="19"/>
       <c r="J69" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K69" s="19"/>
       <c r="L69" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M69" s="23"/>
       <c r="N69" s="25" t="str">
@@ -7994,7 +7883,7 @@
       <c r="P69" s="24"/>
       <c r="Q69" s="27"/>
       <c r="R69" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S69" s="24"/>
     </row>
@@ -8007,30 +7896,30 @@
         <v>45780</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I70" s="19"/>
       <c r="J70" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K70" s="19"/>
       <c r="L70" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M70" s="23"/>
       <c r="N70" s="25" t="str">
@@ -8044,7 +7933,7 @@
       <c r="P70" s="24"/>
       <c r="Q70" s="27"/>
       <c r="R70" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S70" s="24"/>
     </row>
@@ -8057,30 +7946,30 @@
         <v>45780</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F71" s="24" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I71" s="19"/>
       <c r="J71" s="19" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="K71" s="19"/>
       <c r="L71" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M71" s="23"/>
       <c r="N71" s="25" t="str">
@@ -8092,11 +7981,11 @@
         <v>1</v>
       </c>
       <c r="P71" s="24" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="Q71" s="27"/>
       <c r="R71" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S71" s="24"/>
     </row>
@@ -8109,32 +7998,32 @@
         <v>45780</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I72" s="19"/>
       <c r="J72" s="19" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="K72" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L72" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M72" s="23"/>
       <c r="N72" s="25" t="str">
@@ -8146,14 +8035,14 @@
         <v>1</v>
       </c>
       <c r="P72" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q72" s="27"/>
       <c r="R72" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S72" s="24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8165,30 +8054,30 @@
         <v>45780</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I73" s="19"/>
       <c r="J73" s="19" t="s">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="K73" s="19"/>
       <c r="L73" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M73" s="23"/>
       <c r="N73" s="25" t="str">
@@ -8202,7 +8091,7 @@
       <c r="P73" s="24"/>
       <c r="Q73" s="27"/>
       <c r="R73" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S73" s="24"/>
     </row>
@@ -8215,32 +8104,32 @@
         <v>45780</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I74" s="19"/>
       <c r="J74" s="19" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M74" s="23"/>
       <c r="N74" s="25" t="str">
@@ -8252,11 +8141,11 @@
         <v>1</v>
       </c>
       <c r="P74" s="24" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q74" s="27"/>
       <c r="R74" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S74" s="24"/>
     </row>
@@ -8269,30 +8158,30 @@
         <v>45780</v>
       </c>
       <c r="C75" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="G75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F75" s="24" t="s">
-        <v>480</v>
-      </c>
-      <c r="G75" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H75" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I75" s="19"/>
       <c r="J75" s="19" t="s">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="K75" s="19"/>
       <c r="L75" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M75" s="23"/>
       <c r="N75" s="25" t="str">
@@ -8304,11 +8193,11 @@
         <v>1</v>
       </c>
       <c r="P75" s="24" t="s">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="Q75" s="27"/>
       <c r="R75" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S75" s="24"/>
     </row>
@@ -8321,32 +8210,32 @@
         <v>45780</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F76" s="24" t="s">
-        <v>483</v>
+        <v>449</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J76" s="19" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="K76" s="19"/>
       <c r="L76" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M76" s="23"/>
       <c r="N76" s="25" t="str">
@@ -8371,30 +8260,30 @@
         <v>45780</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I77" s="19"/>
       <c r="J77" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K77" s="19"/>
       <c r="L77" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M77" s="23"/>
       <c r="N77" s="25" t="str">
@@ -8406,11 +8295,11 @@
         <v>1</v>
       </c>
       <c r="P77" s="24" t="s">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="Q77" s="27"/>
       <c r="R77" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S77" s="24"/>
     </row>
@@ -8423,30 +8312,30 @@
         <v>45780</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I78" s="19"/>
       <c r="J78" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K78" s="19"/>
       <c r="L78" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M78" s="23"/>
       <c r="N78" s="25" t="n">
@@ -8458,11 +8347,11 @@
         <v>1</v>
       </c>
       <c r="P78" s="24" t="s">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="Q78" s="27"/>
       <c r="R78" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S78" s="24"/>
     </row>
@@ -8475,32 +8364,32 @@
         <v>45780</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I79" s="19"/>
       <c r="J79" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K79" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L79" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M79" s="23"/>
       <c r="N79" s="25" t="str">
@@ -8514,7 +8403,7 @@
       <c r="P79" s="24"/>
       <c r="Q79" s="27"/>
       <c r="R79" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S79" s="24"/>
     </row>
@@ -8527,30 +8416,30 @@
         <v>45780</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I80" s="19"/>
       <c r="J80" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K80" s="19"/>
       <c r="L80" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M80" s="23"/>
       <c r="N80" s="25" t="str">
@@ -8564,10 +8453,10 @@
       <c r="P80" s="24"/>
       <c r="Q80" s="27"/>
       <c r="R80" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S80" s="24" t="s">
-        <v>490</v>
+        <v>456</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8579,32 +8468,32 @@
         <v>45780</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I81" s="19"/>
       <c r="J81" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K81" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M81" s="23"/>
       <c r="N81" s="25" t="str">
@@ -8618,7 +8507,7 @@
       <c r="P81" s="24"/>
       <c r="Q81" s="27"/>
       <c r="R81" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S81" s="24"/>
     </row>
@@ -8631,30 +8520,30 @@
         <v>45780</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I82" s="19"/>
       <c r="J82" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K82" s="19"/>
       <c r="L82" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M82" s="23"/>
       <c r="N82" s="25" t="str">
@@ -8668,7 +8557,7 @@
       <c r="P82" s="24"/>
       <c r="Q82" s="27"/>
       <c r="R82" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S82" s="24"/>
     </row>
@@ -8681,30 +8570,30 @@
         <v>45780</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I83" s="19"/>
       <c r="J83" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K83" s="19"/>
       <c r="L83" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M83" s="23"/>
       <c r="N83" s="25" t="str">
@@ -8718,7 +8607,7 @@
       <c r="P83" s="24"/>
       <c r="Q83" s="27"/>
       <c r="R83" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S83" s="24"/>
     </row>
@@ -8731,30 +8620,30 @@
         <v>45780</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I84" s="19"/>
       <c r="J84" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K84" s="19"/>
       <c r="L84" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M84" s="23"/>
       <c r="N84" s="25" t="str">
@@ -8766,11 +8655,11 @@
         <v>1</v>
       </c>
       <c r="P84" s="24" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="Q84" s="27"/>
       <c r="R84" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S84" s="24"/>
     </row>
@@ -8783,30 +8672,30 @@
         <v>45780</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I85" s="19"/>
       <c r="J85" s="19" t="s">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="K85" s="19"/>
       <c r="L85" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M85" s="23"/>
       <c r="N85" s="25" t="str">
@@ -8820,10 +8709,10 @@
       <c r="P85" s="24"/>
       <c r="Q85" s="27"/>
       <c r="R85" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S85" s="24" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8835,30 +8724,30 @@
         <v>45780</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I86" s="19"/>
       <c r="J86" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K86" s="19"/>
       <c r="L86" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M86" s="23"/>
       <c r="N86" s="25" t="str">
@@ -8872,7 +8761,7 @@
       <c r="P86" s="24"/>
       <c r="Q86" s="27"/>
       <c r="R86" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S86" s="24"/>
     </row>
@@ -8885,30 +8774,30 @@
         <v>45780</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I87" s="19"/>
       <c r="J87" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K87" s="19"/>
       <c r="L87" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M87" s="23"/>
       <c r="N87" s="25" t="str">
@@ -8922,7 +8811,7 @@
       <c r="P87" s="24"/>
       <c r="Q87" s="27"/>
       <c r="R87" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S87" s="24"/>
     </row>
@@ -8935,30 +8824,30 @@
         <v>45780</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I88" s="19"/>
       <c r="J88" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K88" s="19"/>
       <c r="L88" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M88" s="23"/>
       <c r="N88" s="25" t="str">
@@ -8972,7 +8861,7 @@
       <c r="P88" s="24"/>
       <c r="Q88" s="27"/>
       <c r="R88" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S88" s="24"/>
     </row>
@@ -8985,30 +8874,30 @@
         <v>45780</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I89" s="19"/>
       <c r="J89" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K89" s="19"/>
       <c r="L89" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M89" s="23"/>
       <c r="N89" s="25" t="str">
@@ -9022,7 +8911,7 @@
       <c r="P89" s="24"/>
       <c r="Q89" s="27"/>
       <c r="R89" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S89" s="24"/>
     </row>
@@ -9035,30 +8924,30 @@
         <v>45780</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I90" s="19"/>
       <c r="J90" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K90" s="19"/>
       <c r="L90" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M90" s="23"/>
       <c r="N90" s="25" t="str">
@@ -9072,7 +8961,7 @@
       <c r="P90" s="24"/>
       <c r="Q90" s="27"/>
       <c r="R90" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S90" s="24"/>
     </row>
@@ -9085,30 +8974,30 @@
         <v>45780</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I91" s="19"/>
       <c r="J91" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K91" s="19"/>
       <c r="L91" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M91" s="23"/>
       <c r="N91" s="25" t="str">
@@ -9120,11 +9009,11 @@
         <v>1</v>
       </c>
       <c r="P91" s="24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q91" s="27"/>
       <c r="R91" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S91" s="24"/>
     </row>
@@ -9137,30 +9026,30 @@
         <v>45780</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>504</v>
+        <v>470</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I92" s="19"/>
       <c r="J92" s="19" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="K92" s="19"/>
       <c r="L92" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M92" s="23"/>
       <c r="N92" s="25" t="str">
@@ -9174,7 +9063,7 @@
       <c r="P92" s="24"/>
       <c r="Q92" s="27"/>
       <c r="R92" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S92" s="24"/>
     </row>
@@ -9187,32 +9076,32 @@
         <v>45780</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I93" s="19"/>
       <c r="J93" s="19" t="s">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="K93" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L93" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M93" s="23"/>
       <c r="N93" s="25" t="str">
@@ -9224,11 +9113,11 @@
         <v>1</v>
       </c>
       <c r="P93" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q93" s="27"/>
       <c r="R93" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S93" s="24"/>
     </row>
@@ -9241,30 +9130,30 @@
         <v>45780</v>
       </c>
       <c r="C94" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="G94" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D94" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="G94" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H94" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I94" s="19"/>
       <c r="J94" s="19" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="K94" s="19"/>
       <c r="L94" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M94" s="23"/>
       <c r="N94" s="25" t="str">
@@ -9276,11 +9165,11 @@
         <v>1</v>
       </c>
       <c r="P94" s="24" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="Q94" s="27"/>
       <c r="R94" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S94" s="24"/>
     </row>
@@ -9293,32 +9182,32 @@
         <v>45780</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I95" s="19"/>
       <c r="J95" s="19" t="s">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="K95" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L95" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M95" s="23"/>
       <c r="N95" s="25" t="n">
@@ -9330,7 +9219,7 @@
         <v>1</v>
       </c>
       <c r="P95" s="24" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q95" s="27"/>
       <c r="R95" s="19"/>
@@ -9345,24 +9234,24 @@
         <v>45780</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F96" s="24" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H96" s="19"/>
       <c r="I96" s="19"/>
       <c r="J96" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K96" s="19"/>
       <c r="L96" s="19"/>
@@ -9389,30 +9278,30 @@
         <v>45780</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F97" s="24" t="s">
-        <v>512</v>
+        <v>478</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I97" s="19"/>
       <c r="J97" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K97" s="19"/>
       <c r="L97" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M97" s="23"/>
       <c r="N97" s="25" t="str">
@@ -9437,30 +9326,30 @@
         <v>45780</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I98" s="19"/>
       <c r="J98" s="19" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="K98" s="19"/>
       <c r="L98" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M98" s="23"/>
       <c r="N98" s="25" t="str">
@@ -9485,30 +9374,30 @@
         <v>45780</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F99" s="24" t="s">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I99" s="19"/>
       <c r="J99" s="19" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="K99" s="19"/>
       <c r="L99" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M99" s="23"/>
       <c r="N99" s="25" t="str">
@@ -9533,30 +9422,30 @@
         <v>45781</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D100" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="F100" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H100" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E100" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="F100" s="24" t="s">
-        <v>515</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H100" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I100" s="19"/>
       <c r="J100" s="19" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="K100" s="19"/>
       <c r="L100" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M100" s="23"/>
       <c r="N100" s="25" t="n">
@@ -9568,7 +9457,7 @@
         <v>1</v>
       </c>
       <c r="P100" s="24" t="s">
-        <v>517</v>
+        <v>483</v>
       </c>
       <c r="Q100" s="27"/>
       <c r="R100" s="19"/>
@@ -9583,30 +9472,30 @@
         <v>45781</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I101" s="19"/>
       <c r="J101" s="19" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="K101" s="19"/>
       <c r="L101" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M101" s="23"/>
       <c r="N101" s="25" t="str">
@@ -9620,10 +9509,10 @@
       <c r="P101" s="24"/>
       <c r="Q101" s="27"/>
       <c r="R101" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S101" s="24" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9635,30 +9524,30 @@
         <v>45781</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D102" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F102" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="G102" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H102" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E102" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F102" s="24" t="s">
-        <v>520</v>
-      </c>
-      <c r="G102" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="H102" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I102" s="19"/>
       <c r="J102" s="19" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="K102" s="19"/>
       <c r="L102" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M102" s="23"/>
       <c r="N102" s="25" t="str">
@@ -9672,7 +9561,7 @@
       <c r="P102" s="24"/>
       <c r="Q102" s="27"/>
       <c r="R102" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S102" s="24"/>
     </row>
@@ -9685,30 +9574,30 @@
         <v>45781</v>
       </c>
       <c r="C103" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F103" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="G103" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="H103" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="F103" s="24" t="s">
-        <v>521</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H103" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I103" s="19"/>
       <c r="J103" s="19" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="K103" s="19"/>
       <c r="L103" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M103" s="23"/>
       <c r="N103" s="25" t="str">
@@ -9722,7 +9611,7 @@
       <c r="P103" s="24"/>
       <c r="Q103" s="27"/>
       <c r="R103" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S103" s="24"/>
     </row>
@@ -9735,30 +9624,30 @@
         <v>45781</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D104" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F104" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="G104" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E104" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F104" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="G104" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="H104" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I104" s="19"/>
       <c r="J104" s="19" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="K104" s="19"/>
       <c r="L104" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M104" s="23"/>
       <c r="N104" s="25" t="str">
@@ -9772,7 +9661,7 @@
       <c r="P104" s="24"/>
       <c r="Q104" s="27"/>
       <c r="R104" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S104" s="24"/>
     </row>
@@ -9785,30 +9674,30 @@
         <v>45781</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I105" s="19"/>
       <c r="J105" s="19" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="K105" s="19"/>
       <c r="L105" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M105" s="23"/>
       <c r="N105" s="25" t="str">
@@ -9822,7 +9711,7 @@
       <c r="P105" s="24"/>
       <c r="Q105" s="27"/>
       <c r="R105" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S105" s="24"/>
     </row>
@@ -9835,30 +9724,30 @@
         <v>45781</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I106" s="19"/>
       <c r="J106" s="19" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="K106" s="19"/>
       <c r="L106" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M106" s="23"/>
       <c r="N106" s="25" t="n">
@@ -9883,30 +9772,30 @@
         <v>45781</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I107" s="19"/>
       <c r="J107" s="19" t="s">
-        <v>528</v>
+        <v>494</v>
       </c>
       <c r="K107" s="19"/>
       <c r="L107" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M107" s="23"/>
       <c r="N107" s="25" t="str">
@@ -9920,7 +9809,7 @@
       <c r="P107" s="24"/>
       <c r="Q107" s="27"/>
       <c r="R107" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S107" s="24"/>
     </row>
@@ -9933,30 +9822,30 @@
         <v>45781</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I108" s="19"/>
       <c r="J108" s="19" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="K108" s="19"/>
       <c r="L108" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M108" s="23"/>
       <c r="N108" s="25" t="str">
@@ -9968,11 +9857,11 @@
         <v>1</v>
       </c>
       <c r="P108" s="24" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="Q108" s="27"/>
       <c r="R108" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S108" s="24"/>
     </row>
@@ -9985,30 +9874,30 @@
         <v>45781</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I109" s="19"/>
       <c r="J109" s="19" t="s">
-        <v>532</v>
+        <v>498</v>
       </c>
       <c r="K109" s="19"/>
       <c r="L109" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M109" s="23"/>
       <c r="N109" s="25" t="str">
@@ -10022,7 +9911,7 @@
       <c r="P109" s="24"/>
       <c r="Q109" s="27"/>
       <c r="R109" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S109" s="24"/>
     </row>
@@ -10035,30 +9924,30 @@
         <v>45781</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I110" s="19"/>
       <c r="J110" s="19" t="s">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="K110" s="19"/>
       <c r="L110" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M110" s="23"/>
       <c r="N110" s="25" t="str">
@@ -10070,11 +9959,11 @@
         <v>1</v>
       </c>
       <c r="P110" s="24" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q110" s="27"/>
       <c r="R110" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S110" s="24"/>
     </row>
@@ -10087,30 +9976,30 @@
         <v>45781</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F111" s="24" t="s">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I111" s="19"/>
       <c r="J111" s="19" t="s">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="K111" s="19"/>
       <c r="L111" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M111" s="23"/>
       <c r="N111" s="25" t="str">
@@ -10124,7 +10013,7 @@
       <c r="P111" s="24"/>
       <c r="Q111" s="27"/>
       <c r="R111" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S111" s="24"/>
     </row>
@@ -10137,30 +10026,30 @@
         <v>45781</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>536</v>
+        <v>502</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I112" s="19"/>
       <c r="J112" s="19" t="s">
-        <v>537</v>
+        <v>503</v>
       </c>
       <c r="K112" s="19"/>
       <c r="L112" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M112" s="23"/>
       <c r="N112" s="25" t="str">
@@ -10174,7 +10063,7 @@
       <c r="P112" s="24"/>
       <c r="Q112" s="27"/>
       <c r="R112" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S112" s="24"/>
     </row>
@@ -10187,32 +10076,32 @@
         <v>45781</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>538</v>
+        <v>504</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I113" s="19"/>
       <c r="J113" s="19" t="s">
-        <v>539</v>
+        <v>505</v>
       </c>
       <c r="K113" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L113" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M113" s="23"/>
       <c r="N113" s="25" t="n">
@@ -10224,7 +10113,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="24" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q113" s="27"/>
       <c r="R113" s="19"/>
@@ -10239,30 +10128,30 @@
         <v>45781</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I114" s="19"/>
       <c r="J114" s="19" t="s">
-        <v>541</v>
+        <v>507</v>
       </c>
       <c r="K114" s="19"/>
       <c r="L114" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M114" s="23"/>
       <c r="N114" s="25" t="str">
@@ -10276,10 +10165,10 @@
       <c r="P114" s="24"/>
       <c r="Q114" s="27"/>
       <c r="R114" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S114" s="24" t="s">
-        <v>542</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10291,30 +10180,30 @@
         <v>45781</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I115" s="19"/>
       <c r="J115" s="19" t="s">
-        <v>544</v>
+        <v>510</v>
       </c>
       <c r="K115" s="19"/>
       <c r="L115" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M115" s="23"/>
       <c r="N115" s="25" t="str">
@@ -10328,7 +10217,7 @@
       <c r="P115" s="24"/>
       <c r="Q115" s="27"/>
       <c r="R115" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S115" s="24"/>
     </row>
@@ -10341,24 +10230,24 @@
         <v>45781</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H116" s="19"/>
       <c r="I116" s="19"/>
       <c r="J116" s="19" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="K116" s="19"/>
       <c r="L116" s="19"/>
@@ -10385,30 +10274,30 @@
         <v>45782</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H117" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I117" s="19"/>
       <c r="J117" s="19" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="K117" s="19"/>
       <c r="L117" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M117" s="23"/>
       <c r="N117" s="25" t="str">
@@ -10422,7 +10311,7 @@
       <c r="P117" s="24"/>
       <c r="Q117" s="27"/>
       <c r="R117" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S117" s="24"/>
     </row>
@@ -10435,30 +10324,30 @@
         <v>45782</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H118" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I118" s="19"/>
       <c r="J118" s="19" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="K118" s="19"/>
       <c r="L118" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M118" s="23"/>
       <c r="N118" s="25" t="str">
@@ -10470,11 +10359,11 @@
         <v>1</v>
       </c>
       <c r="P118" s="24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q118" s="27"/>
       <c r="R118" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S118" s="24"/>
     </row>
@@ -10487,32 +10376,32 @@
         <v>45782</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H119" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I119" s="19"/>
       <c r="J119" s="19" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="K119" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L119" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M119" s="23"/>
       <c r="N119" s="25" t="str">
@@ -10526,7 +10415,7 @@
       <c r="P119" s="24"/>
       <c r="Q119" s="27"/>
       <c r="R119" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S119" s="24"/>
     </row>
@@ -10539,30 +10428,30 @@
         <v>45782</v>
       </c>
       <c r="C120" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="F120" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="G120" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D120" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="F120" s="24" t="s">
-        <v>550</v>
-      </c>
-      <c r="G120" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H120" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I120" s="19"/>
       <c r="J120" s="19" t="s">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="K120" s="19"/>
       <c r="L120" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M120" s="23"/>
       <c r="N120" s="25" t="str">
@@ -10574,11 +10463,11 @@
         <v>1</v>
       </c>
       <c r="P120" s="24" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q120" s="27"/>
       <c r="R120" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S120" s="24"/>
     </row>
@@ -10591,30 +10480,30 @@
         <v>45782</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I121" s="19"/>
       <c r="J121" s="19" t="s">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="K121" s="19"/>
       <c r="L121" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M121" s="23"/>
       <c r="N121" s="25" t="str">
@@ -10628,7 +10517,7 @@
       <c r="P121" s="24"/>
       <c r="Q121" s="27"/>
       <c r="R121" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S121" s="24"/>
     </row>
@@ -10641,30 +10530,30 @@
         <v>45782</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E122" s="19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>553</v>
+        <v>519</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H122" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I122" s="19"/>
       <c r="J122" s="19" t="s">
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="K122" s="19"/>
       <c r="L122" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M122" s="23"/>
       <c r="N122" s="25" t="str">
@@ -10676,11 +10565,11 @@
         <v>1</v>
       </c>
       <c r="P122" s="24" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q122" s="27"/>
       <c r="R122" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S122" s="24"/>
     </row>
@@ -10693,30 +10582,30 @@
         <v>45782</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>555</v>
+        <v>521</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I123" s="19"/>
       <c r="J123" s="19" t="s">
-        <v>556</v>
+        <v>522</v>
       </c>
       <c r="K123" s="19"/>
       <c r="L123" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M123" s="23"/>
       <c r="N123" s="25" t="str">
@@ -10730,7 +10619,7 @@
       <c r="P123" s="24"/>
       <c r="Q123" s="27"/>
       <c r="R123" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S123" s="24"/>
     </row>
@@ -10743,32 +10632,32 @@
         <v>45782</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>557</v>
+        <v>523</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I124" s="19"/>
       <c r="J124" s="19" t="s">
-        <v>558</v>
+        <v>524</v>
       </c>
       <c r="K124" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L124" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M124" s="23"/>
       <c r="N124" s="25" t="str">
@@ -10780,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="P124" s="24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q124" s="27"/>
       <c r="R124" s="19"/>
@@ -10795,30 +10684,30 @@
         <v>45783</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D125" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F125" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="G125" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E125" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F125" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="G125" s="19" t="s">
-        <v>126</v>
-      </c>
       <c r="H125" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I125" s="19"/>
       <c r="J125" s="19" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="K125" s="19"/>
       <c r="L125" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M125" s="23"/>
       <c r="N125" s="25" t="str">
@@ -10832,7 +10721,7 @@
       <c r="P125" s="24"/>
       <c r="Q125" s="27"/>
       <c r="R125" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S125" s="24"/>
     </row>
@@ -10845,30 +10734,30 @@
         <v>45783</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>561</v>
+        <v>527</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I126" s="19"/>
       <c r="J126" s="19" t="s">
-        <v>562</v>
+        <v>528</v>
       </c>
       <c r="K126" s="19"/>
       <c r="L126" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M126" s="23"/>
       <c r="N126" s="25" t="str">
@@ -10882,7 +10771,7 @@
       <c r="P126" s="24"/>
       <c r="Q126" s="27"/>
       <c r="R126" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S126" s="24"/>
     </row>
@@ -10895,30 +10784,30 @@
         <v>45783</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F127" s="24" t="s">
-        <v>563</v>
+        <v>529</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I127" s="19"/>
       <c r="J127" s="19" t="s">
-        <v>564</v>
+        <v>530</v>
       </c>
       <c r="K127" s="19"/>
       <c r="L127" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M127" s="23"/>
       <c r="N127" s="25" t="str">
@@ -10932,7 +10821,7 @@
       <c r="P127" s="24"/>
       <c r="Q127" s="27"/>
       <c r="R127" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S127" s="24"/>
     </row>
@@ -10945,30 +10834,30 @@
         <v>45783</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D128" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E128" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F128" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="G128" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E128" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F128" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="G128" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="H128" s="19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I128" s="19"/>
       <c r="J128" s="19" t="s">
-        <v>566</v>
+        <v>532</v>
       </c>
       <c r="K128" s="19"/>
       <c r="L128" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M128" s="23"/>
       <c r="N128" s="25" t="str">
@@ -10982,7 +10871,7 @@
       <c r="P128" s="24"/>
       <c r="Q128" s="27"/>
       <c r="R128" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S128" s="24"/>
     </row>
@@ -10995,30 +10884,30 @@
         <v>45783</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F129" s="24" t="s">
-        <v>567</v>
+        <v>533</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I129" s="19"/>
       <c r="J129" s="19" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="K129" s="19"/>
       <c r="L129" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M129" s="23"/>
       <c r="N129" s="25" t="str">
@@ -11032,7 +10921,7 @@
       <c r="P129" s="24"/>
       <c r="Q129" s="27"/>
       <c r="R129" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S129" s="24"/>
     </row>
@@ -11045,30 +10934,30 @@
         <v>45783</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F130" s="24" t="s">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I130" s="19"/>
       <c r="J130" s="19" t="s">
-        <v>570</v>
+        <v>536</v>
       </c>
       <c r="K130" s="19"/>
       <c r="L130" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M130" s="23"/>
       <c r="N130" s="25" t="str">
@@ -11082,7 +10971,7 @@
       <c r="P130" s="24"/>
       <c r="Q130" s="27"/>
       <c r="R130" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S130" s="24"/>
     </row>
@@ -11095,28 +10984,28 @@
         <v>45783</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H131" s="19"/>
       <c r="I131" s="19"/>
       <c r="J131" s="19" t="s">
-        <v>570</v>
+        <v>536</v>
       </c>
       <c r="K131" s="19"/>
       <c r="L131" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M131" s="23"/>
       <c r="N131" s="25" t="str">
@@ -11130,7 +11019,7 @@
       <c r="P131" s="24"/>
       <c r="Q131" s="27"/>
       <c r="R131" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S131" s="24"/>
     </row>
@@ -11143,30 +11032,30 @@
         <v>45783</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D132" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E132" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F132" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="G132" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H132" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E132" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F132" s="24" t="s">
-        <v>572</v>
-      </c>
-      <c r="G132" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="H132" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I132" s="19"/>
       <c r="J132" s="19" t="s">
-        <v>570</v>
+        <v>536</v>
       </c>
       <c r="K132" s="19"/>
       <c r="L132" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M132" s="23"/>
       <c r="N132" s="25" t="str">
@@ -11180,7 +11069,7 @@
       <c r="P132" s="24"/>
       <c r="Q132" s="27"/>
       <c r="R132" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S132" s="24"/>
     </row>
@@ -11193,32 +11082,32 @@
         <v>45783</v>
       </c>
       <c r="C133" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="F133" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="G133" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D133" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E133" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F133" s="24" t="s">
-        <v>573</v>
-      </c>
-      <c r="G133" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H133" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I133" s="19"/>
       <c r="J133" s="19" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="K133" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L133" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M133" s="23"/>
       <c r="N133" s="25" t="str">
@@ -11230,11 +11119,11 @@
         <v>1</v>
       </c>
       <c r="P133" s="24" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q133" s="27"/>
       <c r="R133" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S133" s="24"/>
     </row>
@@ -11247,30 +11136,30 @@
         <v>45783</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D134" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F134" s="24" t="s">
-        <v>574</v>
+        <v>540</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H134" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I134" s="19"/>
       <c r="J134" s="19" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="K134" s="19"/>
       <c r="L134" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M134" s="23"/>
       <c r="N134" s="25" t="str">
@@ -11284,7 +11173,7 @@
       <c r="P134" s="24"/>
       <c r="Q134" s="27"/>
       <c r="R134" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S134" s="24"/>
     </row>
@@ -11297,30 +11186,30 @@
         <v>45783</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F135" s="24" t="s">
-        <v>575</v>
+        <v>541</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I135" s="19"/>
       <c r="J135" s="19" t="s">
-        <v>576</v>
+        <v>542</v>
       </c>
       <c r="K135" s="19"/>
       <c r="L135" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M135" s="23"/>
       <c r="N135" s="25" t="str">
@@ -11332,11 +11221,11 @@
         <v>1</v>
       </c>
       <c r="P135" s="24" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q135" s="27"/>
       <c r="R135" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S135" s="24"/>
     </row>
@@ -11349,30 +11238,30 @@
         <v>45783</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F136" s="24" t="s">
-        <v>577</v>
+        <v>543</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I136" s="19"/>
       <c r="J136" s="19" t="s">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="K136" s="19"/>
       <c r="L136" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M136" s="23"/>
       <c r="N136" s="25" t="str">
@@ -11386,7 +11275,7 @@
       <c r="P136" s="24"/>
       <c r="Q136" s="27"/>
       <c r="R136" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S136" s="24"/>
     </row>
@@ -11399,30 +11288,30 @@
         <v>45783</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D137" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F137" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="G137" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H137" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E137" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F137" s="24" t="s">
-        <v>579</v>
-      </c>
-      <c r="G137" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H137" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I137" s="19"/>
       <c r="J137" s="19" t="s">
-        <v>580</v>
+        <v>546</v>
       </c>
       <c r="K137" s="19"/>
       <c r="L137" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M137" s="23"/>
       <c r="N137" s="25" t="str">
@@ -11436,7 +11325,7 @@
       <c r="P137" s="24"/>
       <c r="Q137" s="27"/>
       <c r="R137" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S137" s="24"/>
     </row>
@@ -11449,32 +11338,32 @@
         <v>45783</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E138" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F138" s="24" t="s">
-        <v>581</v>
+        <v>547</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I138" s="19"/>
       <c r="J138" s="19" t="s">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="K138" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L138" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M138" s="23"/>
       <c r="N138" s="25" t="n">
@@ -11486,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="P138" s="24" t="s">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="Q138" s="27"/>
       <c r="R138" s="19"/>
@@ -11501,30 +11390,30 @@
         <v>45784</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D139" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E139" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F139" s="24" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I139" s="19"/>
       <c r="J139" s="19" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="K139" s="19"/>
       <c r="L139" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M139" s="23"/>
       <c r="N139" s="25" t="str">
@@ -11538,7 +11427,7 @@
       <c r="P139" s="24"/>
       <c r="Q139" s="27"/>
       <c r="R139" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S139" s="24"/>
     </row>
@@ -11551,30 +11440,30 @@
         <v>45784</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F140" s="24" t="s">
-        <v>586</v>
+        <v>552</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I140" s="19"/>
       <c r="J140" s="19" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="K140" s="19"/>
       <c r="L140" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M140" s="23"/>
       <c r="N140" s="25" t="str">
@@ -11586,11 +11475,11 @@
         <v>1</v>
       </c>
       <c r="P140" s="24" t="s">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="Q140" s="27"/>
       <c r="R140" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S140" s="24"/>
     </row>
@@ -11603,30 +11492,30 @@
         <v>45784</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D141" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F141" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="G141" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H141" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E141" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F141" s="24" t="s">
-        <v>588</v>
-      </c>
-      <c r="G141" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="H141" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I141" s="19"/>
       <c r="J141" s="19" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="K141" s="19"/>
       <c r="L141" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M141" s="23"/>
       <c r="N141" s="25" t="str">
@@ -11640,7 +11529,7 @@
       <c r="P141" s="24"/>
       <c r="Q141" s="27"/>
       <c r="R141" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S141" s="24"/>
     </row>
@@ -11653,30 +11542,30 @@
         <v>45784</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D142" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E142" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F142" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="G142" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H142" s="19" t="s">
         <v>83</v>
-      </c>
-      <c r="E142" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F142" s="24" t="s">
-        <v>589</v>
-      </c>
-      <c r="G142" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="H142" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="I142" s="19"/>
       <c r="J142" s="19" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="K142" s="19"/>
       <c r="L142" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M142" s="23"/>
       <c r="N142" s="25" t="str">
@@ -11690,7 +11579,7 @@
       <c r="P142" s="24"/>
       <c r="Q142" s="27"/>
       <c r="R142" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S142" s="24"/>
     </row>
@@ -11703,30 +11592,30 @@
         <v>45784</v>
       </c>
       <c r="C143" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F143" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="G143" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D143" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="F143" s="24" t="s">
-        <v>591</v>
-      </c>
-      <c r="G143" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H143" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I143" s="19"/>
       <c r="J143" s="19" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="K143" s="19"/>
       <c r="L143" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M143" s="23"/>
       <c r="N143" s="25" t="str">
@@ -11740,7 +11629,7 @@
       <c r="P143" s="24"/>
       <c r="Q143" s="27"/>
       <c r="R143" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S143" s="24"/>
     </row>
@@ -11753,30 +11642,30 @@
         <v>45784</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H144" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I144" s="19"/>
       <c r="J144" s="19" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="K144" s="19"/>
       <c r="L144" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M144" s="23"/>
       <c r="N144" s="25" t="str">
@@ -11788,11 +11677,11 @@
         <v>1</v>
       </c>
       <c r="P144" s="24" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q144" s="27"/>
       <c r="R144" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S144" s="24"/>
     </row>
@@ -11805,30 +11694,30 @@
         <v>45784</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E145" s="19" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F145" s="24" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H145" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I145" s="19"/>
       <c r="J145" s="19" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="K145" s="19"/>
       <c r="L145" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M145" s="23"/>
       <c r="N145" s="25" t="str">
@@ -11842,7 +11731,7 @@
       <c r="P145" s="24"/>
       <c r="Q145" s="27"/>
       <c r="R145" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S145" s="24"/>
     </row>
@@ -11855,30 +11744,30 @@
         <v>45784</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>594</v>
+        <v>560</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H146" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I146" s="19"/>
       <c r="J146" s="19" t="s">
-        <v>595</v>
+        <v>561</v>
       </c>
       <c r="K146" s="19"/>
       <c r="L146" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M146" s="23"/>
       <c r="N146" s="25" t="str">
@@ -11892,10 +11781,10 @@
       <c r="P146" s="24"/>
       <c r="Q146" s="27"/>
       <c r="R146" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S146" s="24" t="s">
-        <v>596</v>
+        <v>562</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11907,30 +11796,30 @@
         <v>45784</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D147" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E147" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F147" s="24" t="s">
-        <v>597</v>
+        <v>563</v>
       </c>
       <c r="G147" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H147" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I147" s="19"/>
       <c r="J147" s="19" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="K147" s="19"/>
       <c r="L147" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M147" s="23"/>
       <c r="N147" s="25" t="str">
@@ -11942,11 +11831,11 @@
         <v>1</v>
       </c>
       <c r="P147" s="24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q147" s="27"/>
       <c r="R147" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S147" s="24"/>
     </row>
@@ -11959,32 +11848,32 @@
         <v>45784</v>
       </c>
       <c r="C148" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D148" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E148" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F148" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="G148" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D148" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E148" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="F148" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="G148" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H148" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I148" s="19"/>
       <c r="J148" s="19" t="s">
-        <v>599</v>
+        <v>565</v>
       </c>
       <c r="K148" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L148" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M148" s="23"/>
       <c r="N148" s="25" t="n">
@@ -11996,7 +11885,7 @@
         <v>1</v>
       </c>
       <c r="P148" s="24" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q148" s="27"/>
       <c r="R148" s="19"/>
@@ -12011,30 +11900,30 @@
         <v>45784</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E149" s="19" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F149" s="24" t="s">
-        <v>600</v>
+        <v>566</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H149" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I149" s="19"/>
       <c r="J149" s="19" t="s">
-        <v>601</v>
+        <v>567</v>
       </c>
       <c r="K149" s="19"/>
       <c r="L149" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M149" s="23"/>
       <c r="N149" s="25" t="str">
@@ -12046,11 +11935,11 @@
         <v>1</v>
       </c>
       <c r="P149" s="24" t="s">
-        <v>602</v>
+        <v>568</v>
       </c>
       <c r="Q149" s="27"/>
       <c r="R149" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S149" s="24"/>
     </row>
@@ -12254,7 +12143,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -12264,7 +12153,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
       <c r="I1" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
@@ -12274,7 +12163,7 @@
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B2" s="30" t="n">
         <f aca="false">基准日</f>
@@ -12282,10 +12171,10 @@
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F2" s="16" t="str">
         <f aca="false">"　"&amp;TEXT(期初,"yyyy-mm-dd")&amp;" ~ "&amp;TEXT(期末,"yyyy-mm-dd")&amp;"　　米黄格可改；基准日在【设置】里改，留空即今天"</f>
@@ -12303,7 +12192,7 @@
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
@@ -12321,23 +12210,23 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="35" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="35" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="35" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H5" s="35"/>
       <c r="I5" s="35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J5" s="35"/>
       <c r="K5" s="36"/>
@@ -12378,7 +12267,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="43" t="str">
@@ -12387,15 +12276,15 @@
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="43" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="43" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J7" s="43"/>
       <c r="K7" s="44"/>
@@ -12425,39 +12314,39 @@
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="D10" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="46" t="s">
         <v>65</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>68</v>
       </c>
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L10" s="46" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N10" s="46"/>
     </row>
@@ -13297,36 +13186,36 @@
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="46" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F29" s="46"/>
       <c r="G29" s="46"/>
       <c r="H29" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I29" s="46" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J29" s="46" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K29" s="46" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L29" s="46" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M29" s="46"/>
       <c r="N29" s="46"/>
@@ -13893,23 +13782,23 @@
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B42" s="34"/>
       <c r="C42" s="35" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D42" s="35"/>
       <c r="E42" s="35" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F42" s="35"/>
       <c r="G42" s="35" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H42" s="35"/>
       <c r="I42" s="35" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J42" s="35"/>
       <c r="K42" s="36"/>
@@ -13950,23 +13839,23 @@
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="42" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D44" s="43"/>
       <c r="E44" s="43" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H44" s="43"/>
       <c r="I44" s="43" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J44" s="43"/>
       <c r="K44" s="44"/>
@@ -13977,7 +13866,7 @@
     <row r="45" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="45" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B46" s="45"/>
       <c r="C46" s="45"/>
@@ -13995,43 +13884,43 @@
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="F47" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="I47" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="J47" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="B47" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="46" t="s">
+      <c r="K47" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="L47" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="D47" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="F47" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="G47" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="H47" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="I47" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="J47" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="K47" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="L47" s="46" t="s">
-        <v>278</v>
-      </c>
       <c r="M47" s="46" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N47" s="46"/>
     </row>
@@ -14332,7 +14221,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="45" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B55" s="45"/>
       <c r="C55" s="45"/>
@@ -14345,36 +14234,36 @@
     </row>
     <row r="56" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B56" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="F56" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="G56" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="C56" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="E56" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="F56" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="G56" s="46" t="s">
-        <v>266</v>
-      </c>
       <c r="H56" s="46" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I56" s="46" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="71" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B57" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A57)</f>
@@ -14411,7 +14300,7 @@
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="74" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B58" s="68" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58)</f>
@@ -14448,7 +14337,7 @@
     </row>
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="71" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B59" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A59)</f>
@@ -14485,7 +14374,7 @@
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="74" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B60" s="68" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60)</f>
@@ -14522,7 +14411,7 @@
     </row>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="71" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B61" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A61)</f>
@@ -14559,7 +14448,7 @@
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="74" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B62" s="68" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62)</f>
@@ -14596,7 +14485,7 @@
     </row>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="71" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B63" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A63)</f>
@@ -14633,7 +14522,7 @@
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="74" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B64" s="68" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64)</f>
@@ -14670,7 +14559,7 @@
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="71" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B65" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A65)</f>
@@ -14707,7 +14596,7 @@
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="74" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B66" s="68" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66)</f>
@@ -14744,7 +14633,7 @@
     </row>
     <row r="67" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="71" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B67" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)-SUM(B57:B66)</f>
@@ -14767,7 +14656,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="72" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H67" s="65"/>
       <c r="I67" s="73" t="n">
@@ -14777,7 +14666,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="77" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B68" s="78" t="n">
         <f aca="false">SUM(B57:B67)</f>
@@ -14814,7 +14703,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="45" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B70" s="45"/>
       <c r="C70" s="45"/>
@@ -14827,31 +14716,31 @@
     </row>
     <row r="71" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="46" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D71" s="46" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G71" s="46" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H71" s="46" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I71" s="46" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15350,7 +15239,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="77" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B85" s="78" t="n">
         <f aca="false">SUM(B72:B84)</f>
@@ -15387,7 +15276,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="45" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B87" s="45"/>
       <c r="C87" s="45"/>
@@ -15405,7 +15294,7 @@
     </row>
     <row r="88" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="82" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B88" s="83" t="str">
         <f aca="false">A72</f>
@@ -15944,7 +15833,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -15961,17 +15850,17 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="88" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="16" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -15984,34 +15873,34 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="89" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B5" s="89" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E5" s="89" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F5" s="89" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G5" s="89" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H5" s="89" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I5" s="89" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J5" s="89" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16058,41 +15947,41 @@
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B8" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="E8" s="46" t="s">
         <v>65</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>68</v>
       </c>
       <c r="F8" s="46"/>
       <c r="G8" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I8" s="46" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J8" s="46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K8" s="46" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17276,357 +17165,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF788C5D"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="93" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-    </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="94" t="s">
-        <v>294</v>
-      </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="95" t="s">
-        <v>296</v>
-      </c>
-      <c r="B5" s="96" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="95" t="s">
-        <v>298</v>
-      </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="95" t="s">
-        <v>299</v>
-      </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="95" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>301</v>
-      </c>
-      <c r="F6" s="96"/>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="95" t="s">
-        <v>302</v>
-      </c>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="95" t="s">
-        <v>303</v>
-      </c>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-    </row>
-    <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="97" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-    </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="98" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-    </row>
-    <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="99"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-    </row>
-    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="100" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="98" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-    </row>
-    <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="99"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-    </row>
-    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101" t="s">
-        <v>308</v>
-      </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="101" t="s">
-        <v>309</v>
-      </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-    </row>
-    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="100" t="s">
-        <v>310</v>
-      </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-    </row>
-    <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="97" t="s">
-        <v>311</v>
-      </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="98" t="s">
-        <v>312</v>
-      </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="101" t="s">
-        <v>313</v>
-      </c>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-    </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="99"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-    </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="99"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-    </row>
-    <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="97" t="s">
-        <v>315</v>
-      </c>
-      <c r="B24" s="97"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="97"/>
-    </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="101" t="s">
-        <v>316</v>
-      </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101" t="s">
-        <v>317</v>
-      </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-    </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="101" t="s">
-        <v>318</v>
-      </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101" t="s">
-        <v>319</v>
-      </c>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-    </row>
-    <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="97" t="s">
-        <v>320</v>
-      </c>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="101" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-    </row>
-    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="101" t="s">
-        <v>322</v>
-      </c>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-    </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -17647,39 +17185,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="103" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="104" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="B4" s="105" t="n">
         <v>45784</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="104" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="B5" s="106" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="103" t="s">
-        <v>327</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="107" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="B6" s="108" t="n">
         <f aca="true">IF(B4="",TODAY(),B4)</f>
@@ -17688,27 +17226,27 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="82" t="s">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="C8" s="110" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="E8" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="82" t="s">
-        <v>69</v>
-      </c>
       <c r="G8" s="109" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="111" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B9" s="112" t="str">
         <f aca="false">IFERROR(INDEX($A$9:$A$13,MATCH(1,$C$9:$C$13,0)),IF(1=MAX($C$9:$C$13)+1,"取消",""))</f>
@@ -17719,18 +17257,18 @@
         <v/>
       </c>
       <c r="E9" s="111" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F9" s="111" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G9" s="112" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="111" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B10" s="112" t="str">
         <f aca="false">IFERROR(INDEX($A$9:$A$13,MATCH(2,$C$9:$C$13,0)),IF(2=MAX($C$9:$C$13)+1,"取消",""))</f>
@@ -17741,18 +17279,18 @@
         <v>1</v>
       </c>
       <c r="E10" s="111" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F10" s="111" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G10" s="112" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="111" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B11" s="112" t="str">
         <f aca="false">IFERROR(INDEX($A$9:$A$13,MATCH(3,$C$9:$C$13,0)),IF(3=MAX($C$9:$C$13)+1,"取消",""))</f>
@@ -17763,18 +17301,18 @@
         <v>2</v>
       </c>
       <c r="E11" s="111" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F11" s="111" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G11" s="112" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="111" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B12" s="112" t="str">
         <f aca="false">IFERROR(INDEX($A$9:$A$13,MATCH(4,$C$9:$C$13,0)),IF(4=MAX($C$9:$C$13)+1,"取消",""))</f>
@@ -17785,18 +17323,18 @@
         <v>3</v>
       </c>
       <c r="E12" s="111" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F12" s="111" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G12" s="112" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="111" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B13" s="112" t="str">
         <f aca="false">IFERROR(INDEX($A$9:$A$13,MATCH(5,$C$9:$C$13,0)),IF(5=MAX($C$9:$C$13)+1,"取消",""))</f>
@@ -17807,10 +17345,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="111" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F13" s="111" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17819,120 +17357,120 @@
         <v/>
       </c>
       <c r="E14" s="111" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F14" s="111" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="111" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="103" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="E16" s="111" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="111" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="111" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F18" s="111" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="111" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="111" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="111" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="113" t="s">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="E24" s="113" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="109" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="E25" s="114" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F25" s="114" t="s">
+        <v>272</v>
+      </c>
+      <c r="G25" s="114" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="114" t="s">
+        <v>273</v>
+      </c>
+      <c r="I25" s="114" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="114" t="s">
+        <v>98</v>
+      </c>
+      <c r="K25" s="114" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="114" t="s">
+        <v>274</v>
+      </c>
+      <c r="M25" s="114" t="s">
+        <v>307</v>
+      </c>
+      <c r="N25" s="114" t="s">
         <v>275</v>
       </c>
-      <c r="G25" s="114" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="114" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="114" t="s">
-        <v>90</v>
-      </c>
-      <c r="J25" s="114" t="s">
-        <v>101</v>
-      </c>
-      <c r="K25" s="114" t="s">
-        <v>103</v>
-      </c>
-      <c r="L25" s="114" t="s">
-        <v>277</v>
-      </c>
-      <c r="M25" s="114" t="s">
-        <v>341</v>
-      </c>
-      <c r="N25" s="114" t="s">
-        <v>278</v>
-      </c>
       <c r="O25" s="114" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="P25" s="114" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="112" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="B26" s="115" t="n">
         <f aca="false">基准日</f>
@@ -17993,7 +17531,7 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="112" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="B27" s="115" t="n">
         <f aca="false">基准日-WEEKDAY(基准日,2)+1</f>
@@ -18054,7 +17592,7 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="112" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B28" s="115" t="n">
         <f aca="false">DATE(YEAR(基准日),MONTH(基准日),1)</f>
@@ -18115,7 +17653,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="112" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="B29" s="115" t="n">
         <f aca="false">DATE(2000,1,1)</f>
@@ -18176,7 +17714,7 @@
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="112" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="B30" s="115" t="n">
         <f aca="false">INDEX(B26:B29,MATCH(仪表盘!$E$2,A26:A29,0))</f>

--- a/works/repair-ledger/repair-ledger-sample.xlsx
+++ b/works/repair-ledger/repair-ledger-sample.xlsx
@@ -12058,11 +12058,6 @@
       <formula>$R7="不满意"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:S2006">
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
-      <formula>AND($F7&lt;&gt;"",MOD(ROW(),2)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation allowBlank="true" errorStyle="stop" errorTitle="今日休息" operator="between" prompt="选「休息」后，跟进人下拉里不再出现这位师傅。" promptTitle="今日休息" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="H3:L3" type="list">
       <formula1>"休息,上班"</formula1>
@@ -12404,53 +12399,53 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="str">
+      <c r="A12" s="47" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[单据编号],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>公-东大门-0501-02</v>
       </c>
-      <c r="B12" s="54" t="str">
+      <c r="B12" s="48" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[类型],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>公区</v>
       </c>
-      <c r="C12" s="54" t="str">
+      <c r="C12" s="48" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[楼栋],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>公共区域</v>
       </c>
-      <c r="D12" s="54" t="str">
+      <c r="D12" s="48" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[房号/位置],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>东大门</v>
       </c>
-      <c r="E12" s="55" t="str">
+      <c r="E12" s="49" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[报修问题描述],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>门岗天花受潮破损修缮</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="54" t="str">
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="48" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[维修类别],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>墙地饰面</v>
       </c>
-      <c r="I12" s="53" t="str">
+      <c r="I12" s="47" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[跟进人1],$P12-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P12-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P12-ROW(工单[#Headers]))))</f>
         <v>刘师傅</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="50" t="n">
         <f aca="false">IF($P12=0,"",INDEX(工单[报修日期],$P12-ROW(工单[#Headers])))</f>
         <v>45778</v>
       </c>
-      <c r="K12" s="57" t="n">
+      <c r="K12" s="51" t="n">
         <f aca="false">IF($P12=0,"",INDEX(工单[处理天数],$P12-ROW(工单[#Headers])))</f>
         <v>6</v>
       </c>
-      <c r="L12" s="54" t="str">
+      <c r="L12" s="48" t="str">
         <f aca="false">IF($P12=0,"",IF(INDEX(工单[完成情况],$P12-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P12-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M12" s="55" t="str">
+      <c r="M12" s="49" t="str">
         <f aca="false">IF($P12=0,"",INDEX(工单[维修备注],$P12-ROW(工单[#Headers]))&amp;"")</f>
         <v>已补洞批腻子，待干燥后打磨刷乳胶漆</v>
       </c>
-      <c r="N12" s="55"/>
+      <c r="N12" s="49"/>
       <c r="P12" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),2)),100000),0)</f>
         <v>39</v>
@@ -12510,53 +12505,53 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="str">
+      <c r="A14" s="47" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[单据编号],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>8-1602-0501</v>
       </c>
-      <c r="B14" s="54" t="str">
+      <c r="B14" s="48" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[类型],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="C14" s="54" t="str">
+      <c r="C14" s="48" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[楼栋],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>8栋</v>
       </c>
-      <c r="D14" s="54" t="str">
+      <c r="D14" s="48" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[房号/位置],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>1602</v>
       </c>
-      <c r="E14" s="55" t="str">
+      <c r="E14" s="49" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[报修问题描述],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>客厅空调管冷凝水滴落</v>
       </c>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="54" t="str">
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="48" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[维修类别],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>空调暖通</v>
       </c>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="47" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[跟进人1],$P14-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P14-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P14-ROW(工单[#Headers]))))</f>
         <v/>
       </c>
-      <c r="J14" s="56" t="n">
+      <c r="J14" s="50" t="n">
         <f aca="false">IF($P14=0,"",INDEX(工单[报修日期],$P14-ROW(工单[#Headers])))</f>
         <v>45778</v>
       </c>
-      <c r="K14" s="57" t="n">
+      <c r="K14" s="51" t="n">
         <f aca="false">IF($P14=0,"",INDEX(工单[处理天数],$P14-ROW(工单[#Headers])))</f>
         <v>6</v>
       </c>
-      <c r="L14" s="54" t="str">
+      <c r="L14" s="48" t="str">
         <f aca="false">IF($P14=0,"",IF(INDEX(工单[完成情况],$P14-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P14-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M14" s="55" t="str">
+      <c r="M14" s="49" t="str">
         <f aca="false">IF($P14=0,"",INDEX(工单[维修备注],$P14-ROW(工单[#Headers]))&amp;"")</f>
         <v>需先由第三方单位为楼上住户空调管加装保温棉</v>
       </c>
-      <c r="N14" s="55"/>
+      <c r="N14" s="49"/>
       <c r="P14" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),4)),100000),0)</f>
         <v>14</v>
@@ -12616,53 +12611,53 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="53" t="str">
+      <c r="A16" s="47" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[单据编号],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-2504-0501</v>
       </c>
-      <c r="B16" s="54" t="str">
+      <c r="B16" s="48" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[类型],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="C16" s="54" t="str">
+      <c r="C16" s="48" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[楼栋],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>6栋</v>
       </c>
-      <c r="D16" s="54" t="str">
+      <c r="D16" s="48" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[房号/位置],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>2504</v>
       </c>
-      <c r="E16" s="55" t="str">
+      <c r="E16" s="49" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[报修问题描述],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>空调开机后室内机滴水</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="54" t="str">
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="48" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[维修类别],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>空调暖通</v>
       </c>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="47" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[跟进人1],$P16-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P16-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P16-ROW(工单[#Headers]))))</f>
         <v>刘师傅、张师傅</v>
       </c>
-      <c r="J16" s="56" t="n">
+      <c r="J16" s="50" t="n">
         <f aca="false">IF($P16=0,"",INDEX(工单[报修日期],$P16-ROW(工单[#Headers])))</f>
         <v>45778</v>
       </c>
-      <c r="K16" s="57" t="n">
+      <c r="K16" s="51" t="n">
         <f aca="false">IF($P16=0,"",INDEX(工单[处理天数],$P16-ROW(工单[#Headers])))</f>
         <v>6</v>
       </c>
-      <c r="L16" s="54" t="str">
+      <c r="L16" s="48" t="str">
         <f aca="false">IF($P16=0,"",IF(INDEX(工单[完成情况],$P16-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P16-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M16" s="55" t="str">
+      <c r="M16" s="49" t="str">
         <f aca="false">IF($P16=0,"",INDEX(工单[维修备注],$P16-ROW(工单[#Headers]))&amp;"")</f>
         <v>需重新包扎保温棉，待料处理</v>
       </c>
-      <c r="N16" s="55"/>
+      <c r="N16" s="49"/>
       <c r="P16" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),6)),100000),0)</f>
         <v>8</v>
@@ -12722,53 +12717,53 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="str">
+      <c r="A18" s="47" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[单据编号],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>5-1501-0502</v>
       </c>
-      <c r="B18" s="54" t="str">
+      <c r="B18" s="48" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[类型],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="C18" s="54" t="str">
+      <c r="C18" s="48" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[楼栋],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>5栋</v>
       </c>
-      <c r="D18" s="54" t="str">
+      <c r="D18" s="48" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[房号/位置],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>1501</v>
       </c>
-      <c r="E18" s="55" t="str">
+      <c r="E18" s="49" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[报修问题描述],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>主卧外墙渗水，墙纸发霉</v>
       </c>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="54" t="str">
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="48" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[维修类别],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>渗漏防水</v>
       </c>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="47" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[跟进人1],$P18-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P18-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P18-ROW(工单[#Headers]))))</f>
         <v>陈师傅</v>
       </c>
-      <c r="J18" s="56" t="n">
+      <c r="J18" s="50" t="n">
         <f aca="false">IF($P18=0,"",INDEX(工单[报修日期],$P18-ROW(工单[#Headers])))</f>
         <v>45779</v>
       </c>
-      <c r="K18" s="57" t="n">
+      <c r="K18" s="51" t="n">
         <f aca="false">IF($P18=0,"",INDEX(工单[处理天数],$P18-ROW(工单[#Headers])))</f>
         <v>5</v>
       </c>
-      <c r="L18" s="54" t="str">
+      <c r="L18" s="48" t="str">
         <f aca="false">IF($P18=0,"",IF(INDEX(工单[完成情况],$P18-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P18-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M18" s="55" t="str">
+      <c r="M18" s="49" t="str">
         <f aca="false">IF($P18=0,"",INDEX(工单[维修备注],$P18-ROW(工单[#Headers]))&amp;"")</f>
         <v>已现场拍照留证，待后续协商处理（业主意向使用公共维修资金）</v>
       </c>
-      <c r="N18" s="55"/>
+      <c r="N18" s="49"/>
       <c r="P18" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),8)),100000),0)</f>
         <v>51</v>
@@ -12828,53 +12823,53 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="53" t="str">
+      <c r="A20" s="47" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[单据编号],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>5-1602-0502</v>
       </c>
-      <c r="B20" s="54" t="str">
+      <c r="B20" s="48" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[类型],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="C20" s="54" t="str">
+      <c r="C20" s="48" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[楼栋],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>5栋</v>
       </c>
-      <c r="D20" s="54" t="str">
+      <c r="D20" s="48" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[房号/位置],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>1602</v>
       </c>
-      <c r="E20" s="55" t="str">
+      <c r="E20" s="49" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[报修问题描述],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>次卧外墙窗边渗水</v>
       </c>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="54" t="str">
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="48" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[维修类别],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>渗漏防水</v>
       </c>
-      <c r="I20" s="53" t="str">
+      <c r="I20" s="47" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[跟进人1],$P20-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P20-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P20-ROW(工单[#Headers]))))</f>
         <v>李师傅</v>
       </c>
-      <c r="J20" s="56" t="n">
+      <c r="J20" s="50" t="n">
         <f aca="false">IF($P20=0,"",INDEX(工单[报修日期],$P20-ROW(工单[#Headers])))</f>
         <v>45779</v>
       </c>
-      <c r="K20" s="57" t="n">
+      <c r="K20" s="51" t="n">
         <f aca="false">IF($P20=0,"",INDEX(工单[处理天数],$P20-ROW(工单[#Headers])))</f>
         <v>5</v>
       </c>
-      <c r="L20" s="54" t="str">
+      <c r="L20" s="48" t="str">
         <f aca="false">IF($P20=0,"",IF(INDEX(工单[完成情况],$P20-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P20-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M20" s="55" t="str">
+      <c r="M20" s="49" t="str">
         <f aca="false">IF($P20=0,"",INDEX(工单[维修备注],$P20-ROW(工单[#Headers]))&amp;"")</f>
         <v>已查看，业主要求先处理室内墙面，再排查渗水点并尽快修复</v>
       </c>
-      <c r="N20" s="55"/>
+      <c r="N20" s="49"/>
       <c r="P20" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),10)),100000),0)</f>
         <v>42</v>
@@ -12934,53 +12929,53 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="53" t="str">
+      <c r="A22" s="47" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[单据编号],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-2802-0503</v>
       </c>
-      <c r="B22" s="54" t="str">
+      <c r="B22" s="48" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[类型],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="C22" s="54" t="str">
+      <c r="C22" s="48" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[楼栋],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>6栋</v>
       </c>
-      <c r="D22" s="54" t="str">
+      <c r="D22" s="48" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[房号/位置],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>2802</v>
       </c>
-      <c r="E22" s="55" t="str">
+      <c r="E22" s="49" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[报修问题描述],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>连续下雨后阳台墙面渗水</v>
       </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="54" t="str">
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="48" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[维修类别],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>渗漏防水</v>
       </c>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="47" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[跟进人1],$P22-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P22-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P22-ROW(工单[#Headers]))))</f>
         <v>陈师傅</v>
       </c>
-      <c r="J22" s="56" t="n">
+      <c r="J22" s="50" t="n">
         <f aca="false">IF($P22=0,"",INDEX(工单[报修日期],$P22-ROW(工单[#Headers])))</f>
         <v>45780</v>
       </c>
-      <c r="K22" s="57" t="n">
+      <c r="K22" s="51" t="n">
         <f aca="false">IF($P22=0,"",INDEX(工单[处理天数],$P22-ROW(工单[#Headers])))</f>
         <v>4</v>
       </c>
-      <c r="L22" s="54" t="str">
+      <c r="L22" s="48" t="str">
         <f aca="false">IF($P22=0,"",IF(INDEX(工单[完成情况],$P22-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P22-ROW(工单[#Headers]))))</f>
         <v>跟进中</v>
       </c>
-      <c r="M22" s="55" t="str">
+      <c r="M22" s="49" t="str">
         <f aca="false">IF($P22=0,"",INDEX(工单[维修备注],$P22-ROW(工单[#Headers]))&amp;"")</f>
         <v>已拍照留证，待联系防水单位复查</v>
       </c>
-      <c r="N22" s="55"/>
+      <c r="N22" s="49"/>
       <c r="P22" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),12)),100000),0)</f>
         <v>95</v>
@@ -13040,53 +13035,53 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="53" t="str">
+      <c r="A24" s="47" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[单据编号],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>5-货梯-0504</v>
       </c>
-      <c r="B24" s="54" t="str">
+      <c r="B24" s="48" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[类型],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>公区</v>
       </c>
-      <c r="C24" s="54" t="str">
+      <c r="C24" s="48" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[楼栋],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>5栋</v>
       </c>
-      <c r="D24" s="54" t="str">
+      <c r="D24" s="48" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[房号/位置],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>货梯</v>
       </c>
-      <c r="E24" s="55" t="str">
+      <c r="E24" s="49" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[报修问题描述],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>5栋货梯空调不凉</v>
       </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="54" t="str">
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="48" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[维修类别],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v>空调暖通</v>
       </c>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="47" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[跟进人1],$P24-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$P24-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$P24-ROW(工单[#Headers]))))</f>
         <v/>
       </c>
-      <c r="J24" s="56" t="n">
+      <c r="J24" s="50" t="n">
         <f aca="false">IF($P24=0,"",INDEX(工单[报修日期],$P24-ROW(工单[#Headers])))</f>
         <v>45781</v>
       </c>
-      <c r="K24" s="57" t="n">
+      <c r="K24" s="51" t="n">
         <f aca="false">IF($P24=0,"",INDEX(工单[处理天数],$P24-ROW(工单[#Headers])))</f>
         <v>3</v>
       </c>
-      <c r="L24" s="54" t="str">
+      <c r="L24" s="48" t="str">
         <f aca="false">IF($P24=0,"",IF(INDEX(工单[完成情况],$P24-ROW(工单[#Headers]))="","没填状态",INDEX(工单[完成情况],$P24-ROW(工单[#Headers]))))</f>
         <v>没填状态</v>
       </c>
-      <c r="M24" s="55" t="str">
+      <c r="M24" s="49" t="str">
         <f aca="false">IF($P24=0,"",INDEX(工单[维修备注],$P24-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="N24" s="55"/>
+      <c r="N24" s="49"/>
       <c r="P24" s="52" t="n">
         <f aca="false">IFERROR(MOD(SUMPRODUCT(LARGE((工单[完成情况]&lt;&gt;"已完成")*ISNUMBER(工单[处理天数])*((0&amp;工单[处理天数])*100000+ROW(工单[处理天数])),14)),100000),0)</f>
         <v>116</v>
@@ -13275,50 +13270,50 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="54" t="str">
+      <c r="A31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[楼栋],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>8栋</v>
       </c>
-      <c r="B31" s="54" t="str">
+      <c r="B31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[房号/位置],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>1501</v>
       </c>
-      <c r="C31" s="59" t="n">
+      <c r="C31" s="58" t="n">
         <f aca="false">IF($Q31=0,"",COUNTIFS(工单[楼栋],A31,工单[房号/位置],B31))</f>
         <v>3</v>
       </c>
-      <c r="D31" s="56" t="n">
+      <c r="D31" s="50" t="n">
         <f aca="false">IF($Q31=0,"",INDEX(工单[报修日期],$Q31-ROW(工单[#Headers])))</f>
         <v>45784</v>
       </c>
-      <c r="E31" s="55" t="str">
+      <c r="E31" s="49" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[报修问题描述],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>想挂电视需要打孔</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="54" t="str">
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[维修类别],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>其他</v>
       </c>
-      <c r="I31" s="54" t="str">
+      <c r="I31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[跟进人1],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>张师傅</v>
       </c>
-      <c r="J31" s="54" t="str">
+      <c r="J31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[完成情况],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="K31" s="54" t="str">
+      <c r="K31" s="48" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[维修评价],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L31" s="55" t="str">
+      <c r="L31" s="49" t="str">
         <f aca="false">IF($Q31=0,"",INDEX(工单[维修备注],$Q31-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="49"/>
       <c r="P31" s="52" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(LARGE((工单[该户第几次]=2)*ROW(工单[该户第几次]),2)),0)</f>
         <v>132</v>
@@ -13383,50 +13378,50 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="54" t="str">
+      <c r="A33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[楼栋],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>5栋</v>
       </c>
-      <c r="B33" s="54" t="str">
+      <c r="B33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[房号/位置],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>503</v>
       </c>
-      <c r="C33" s="59" t="n">
+      <c r="C33" s="58" t="n">
         <f aca="false">IF($Q33=0,"",COUNTIFS(工单[楼栋],A33,工单[房号/位置],B33))</f>
         <v>2</v>
       </c>
-      <c r="D33" s="56" t="n">
+      <c r="D33" s="50" t="n">
         <f aca="false">IF($Q33=0,"",INDEX(工单[报修日期],$Q33-ROW(工单[#Headers])))</f>
         <v>45779</v>
       </c>
-      <c r="E33" s="55" t="str">
+      <c r="E33" s="49" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[报修问题描述],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>厨房、卫生间门槛石松动</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="54" t="str">
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[维修类别],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>墙地饰面</v>
       </c>
-      <c r="I33" s="54" t="str">
+      <c r="I33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[跟进人1],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>李师傅</v>
       </c>
-      <c r="J33" s="54" t="str">
+      <c r="J33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[完成情况],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="K33" s="54" t="str">
+      <c r="K33" s="48" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[维修评价],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L33" s="55" t="str">
+      <c r="L33" s="49" t="str">
         <f aca="false">IF($Q33=0,"",INDEX(工单[维修备注],$Q33-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
       <c r="P33" s="52" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(LARGE((工单[该户第几次]=2)*ROW(工单[该户第几次]),4)),0)</f>
         <v>55</v>
@@ -13491,50 +13486,50 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="54" t="str">
+      <c r="A35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[楼栋],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="B35" s="54" t="str">
+      <c r="B35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[房号/位置],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="C35" s="59" t="str">
+      <c r="C35" s="58" t="str">
         <f aca="false">IF($Q35=0,"",COUNTIFS(工单[楼栋],A35,工单[房号/位置],B35))</f>
         <v/>
       </c>
-      <c r="D35" s="56" t="str">
+      <c r="D35" s="50" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[报修日期],$Q35-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="E35" s="55" t="str">
+      <c r="E35" s="49" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[报修问题描述],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="54" t="str">
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[维修类别],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="I35" s="54" t="str">
+      <c r="I35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[跟进人1],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="J35" s="54" t="str">
+      <c r="J35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[完成情况],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="K35" s="54" t="str">
+      <c r="K35" s="48" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[维修评价],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="L35" s="55" t="str">
+      <c r="L35" s="49" t="str">
         <f aca="false">IF($Q35=0,"",INDEX(工单[维修备注],$Q35-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M35" s="55"/>
-      <c r="N35" s="55"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
       <c r="P35" s="52" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(LARGE((工单[该户第几次]=2)*ROW(工单[该户第几次]),6)),0)</f>
         <v>0</v>
@@ -13599,50 +13594,50 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54" t="str">
+      <c r="A37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[楼栋],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="B37" s="54" t="str">
+      <c r="B37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[房号/位置],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="C37" s="59" t="str">
+      <c r="C37" s="58" t="str">
         <f aca="false">IF($Q37=0,"",COUNTIFS(工单[楼栋],A37,工单[房号/位置],B37))</f>
         <v/>
       </c>
-      <c r="D37" s="56" t="str">
+      <c r="D37" s="50" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[报修日期],$Q37-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="E37" s="55" t="str">
+      <c r="E37" s="49" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[报修问题描述],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="54" t="str">
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[维修类别],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="I37" s="54" t="str">
+      <c r="I37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[跟进人1],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="J37" s="54" t="str">
+      <c r="J37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[完成情况],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="K37" s="54" t="str">
+      <c r="K37" s="48" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[维修评价],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="L37" s="55" t="str">
+      <c r="L37" s="49" t="str">
         <f aca="false">IF($Q37=0,"",INDEX(工单[维修备注],$Q37-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
       <c r="P37" s="52" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(LARGE((工单[该户第几次]=2)*ROW(工单[该户第几次]),8)),0)</f>
         <v>0</v>
@@ -13707,50 +13702,50 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="54" t="str">
+      <c r="A39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[楼栋],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="B39" s="54" t="str">
+      <c r="B39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[房号/位置],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="C39" s="59" t="str">
+      <c r="C39" s="58" t="str">
         <f aca="false">IF($Q39=0,"",COUNTIFS(工单[楼栋],A39,工单[房号/位置],B39))</f>
         <v/>
       </c>
-      <c r="D39" s="56" t="str">
+      <c r="D39" s="50" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[报修日期],$Q39-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="E39" s="55" t="str">
+      <c r="E39" s="49" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[报修问题描述],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="54" t="str">
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[维修类别],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="I39" s="54" t="str">
+      <c r="I39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[跟进人1],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="J39" s="54" t="str">
+      <c r="J39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[完成情况],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="K39" s="54" t="str">
+      <c r="K39" s="48" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[维修评价],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="L39" s="55" t="str">
+      <c r="L39" s="49" t="str">
         <f aca="false">IF($Q39=0,"",INDEX(工单[维修备注],$Q39-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="49"/>
       <c r="P39" s="52" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(LARGE((工单[该户第几次]=2)*ROW(工单[该户第几次]),10)),0)</f>
         <v>0</v>
@@ -13980,59 +13975,59 @@
       <c r="N48" s="63"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="67" t="str">
+      <c r="A49" s="63" t="str">
         <f aca="false">IF(INDEX(设置!$F$26:$F$30,MATCH(2,设置!$P$26:$P$30,0))=0,"—","第 2 名")</f>
         <v>第 2 名</v>
       </c>
-      <c r="B49" s="67" t="str">
+      <c r="B49" s="63" t="str">
         <f aca="false">INDEX(设置!$E$26:$E$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>李师傅</v>
       </c>
-      <c r="C49" s="68" t="n">
+      <c r="C49" s="64" t="n">
         <f aca="false">INDEX(设置!$F$26:$F$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>40</v>
       </c>
-      <c r="D49" s="68" t="n">
+      <c r="D49" s="64" t="n">
         <f aca="false">INDEX(设置!$G$26:$G$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>33</v>
       </c>
-      <c r="E49" s="68" t="n">
+      <c r="E49" s="64" t="n">
         <f aca="false">INDEX(设置!$H$26:$H$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>7</v>
       </c>
-      <c r="F49" s="69" t="n">
+      <c r="F49" s="65" t="n">
         <f aca="false">IFERROR(D49/C49,"")</f>
         <v>0.825</v>
       </c>
-      <c r="G49" s="68" t="n">
+      <c r="G49" s="64" t="n">
         <f aca="false">INDEX(设置!$I$26:$I$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>32</v>
       </c>
-      <c r="H49" s="68" t="n">
+      <c r="H49" s="64" t="n">
         <f aca="false">INDEX(设置!$J$26:$J$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>4</v>
       </c>
-      <c r="I49" s="68" t="n">
+      <c r="I49" s="64" t="n">
         <f aca="false">INDEX(设置!$K$26:$K$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>0</v>
       </c>
-      <c r="J49" s="68" t="n">
+      <c r="J49" s="64" t="n">
         <f aca="false">INDEX(设置!$L$26:$L$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>0</v>
       </c>
-      <c r="K49" s="69" t="n">
+      <c r="K49" s="65" t="n">
         <f aca="false">IFERROR((G49+H49)/SUM(G49:J49),"")</f>
         <v>1</v>
       </c>
-      <c r="L49" s="70" t="n">
+      <c r="L49" s="66" t="n">
         <f aca="false">INDEX(设置!$N$26:$N$30,MATCH(2,设置!$P$26:$P$30,0))</f>
         <v>97.8</v>
       </c>
-      <c r="M49" s="67" t="str">
+      <c r="M49" s="63" t="str">
         <f aca="false">IFERROR(INDEX(工单台账!$H$4:$L$4,MATCH(B49,工单台账!$H$2:$L$2,0)),"")</f>
         <v>在岗 7 单</v>
       </c>
-      <c r="N49" s="67"/>
+      <c r="N49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="63" t="str">
@@ -14090,59 +14085,59 @@
       <c r="N50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="67" t="str">
+      <c r="A51" s="63" t="str">
         <f aca="false">IF(INDEX(设置!$F$26:$F$30,MATCH(4,设置!$P$26:$P$30,0))=0,"—","第 4 名")</f>
         <v>第 4 名</v>
       </c>
-      <c r="B51" s="67" t="str">
+      <c r="B51" s="63" t="str">
         <f aca="false">INDEX(设置!$E$26:$E$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>刘师傅</v>
       </c>
-      <c r="C51" s="68" t="n">
+      <c r="C51" s="64" t="n">
         <f aca="false">INDEX(设置!$F$26:$F$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>13</v>
       </c>
-      <c r="D51" s="68" t="n">
+      <c r="D51" s="64" t="n">
         <f aca="false">INDEX(设置!$G$26:$G$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>10</v>
       </c>
-      <c r="E51" s="68" t="n">
+      <c r="E51" s="64" t="n">
         <f aca="false">INDEX(设置!$H$26:$H$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>3</v>
       </c>
-      <c r="F51" s="69" t="n">
+      <c r="F51" s="65" t="n">
         <f aca="false">IFERROR(D51/C51,"")</f>
         <v>0.769230769230769</v>
       </c>
-      <c r="G51" s="68" t="n">
+      <c r="G51" s="64" t="n">
         <f aca="false">INDEX(设置!$I$26:$I$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>8</v>
       </c>
-      <c r="H51" s="68" t="n">
+      <c r="H51" s="64" t="n">
         <f aca="false">INDEX(设置!$J$26:$J$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>1</v>
       </c>
-      <c r="I51" s="68" t="n">
+      <c r="I51" s="64" t="n">
         <f aca="false">INDEX(设置!$K$26:$K$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>0</v>
       </c>
-      <c r="J51" s="68" t="n">
+      <c r="J51" s="64" t="n">
         <f aca="false">INDEX(设置!$L$26:$L$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>0</v>
       </c>
-      <c r="K51" s="69" t="n">
+      <c r="K51" s="65" t="n">
         <f aca="false">IFERROR((G51+H51)/SUM(G51:J51),"")</f>
         <v>1</v>
       </c>
-      <c r="L51" s="70" t="n">
+      <c r="L51" s="66" t="n">
         <f aca="false">INDEX(设置!$N$26:$N$30,MATCH(4,设置!$P$26:$P$30,0))</f>
         <v>97.8</v>
       </c>
-      <c r="M51" s="67" t="str">
+      <c r="M51" s="63" t="str">
         <f aca="false">IFERROR(INDEX(工单台账!$H$4:$L$4,MATCH(B51,工单台账!$H$2:$L$2,0)),"")</f>
         <v>在岗 3 单</v>
       </c>
-      <c r="N51" s="67"/>
+      <c r="N51" s="63"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="63" t="str">
@@ -14299,38 +14294,38 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="B58" s="68" t="n">
+      <c r="B58" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58)</f>
         <v>27</v>
       </c>
-      <c r="C58" s="68" t="n">
+      <c r="C58" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[完成情况],"已完成")</f>
         <v>24</v>
       </c>
-      <c r="D58" s="68" t="n">
+      <c r="D58" s="64" t="n">
         <f aca="false">B58-C58</f>
         <v>3</v>
       </c>
-      <c r="E58" s="69" t="n">
+      <c r="E58" s="65" t="n">
         <f aca="false">IFERROR(C58/B58,"")</f>
         <v>0.888888888888889</v>
       </c>
-      <c r="F58" s="69" t="n">
+      <c r="F58" s="65" t="n">
         <f aca="false">IFERROR(B58/$B$68,"")</f>
         <v>0.188811188811189</v>
       </c>
-      <c r="G58" s="75" t="str">
+      <c r="G58" s="72" t="str">
         <f aca="false">IFERROR(SUMIFS(工单[处理天数],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;")/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;"),"-")</f>
         <v>-</v>
       </c>
-      <c r="H58" s="69" t="n">
+      <c r="H58" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I58" s="76" t="n">
+      <c r="I58" s="73" t="n">
         <f aca="false">SUMIFS(工单[耗材费(元)],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A58)</f>
         <v>0</v>
       </c>
@@ -14373,38 +14368,38 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="74" t="s">
+      <c r="A60" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="B60" s="68" t="n">
+      <c r="B60" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60)</f>
         <v>19</v>
       </c>
-      <c r="C60" s="68" t="n">
+      <c r="C60" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[完成情况],"已完成")</f>
         <v>14</v>
       </c>
-      <c r="D60" s="68" t="n">
+      <c r="D60" s="64" t="n">
         <f aca="false">B60-C60</f>
         <v>5</v>
       </c>
-      <c r="E60" s="69" t="n">
+      <c r="E60" s="65" t="n">
         <f aca="false">IFERROR(C60/B60,"")</f>
         <v>0.736842105263158</v>
       </c>
-      <c r="F60" s="69" t="n">
+      <c r="F60" s="65" t="n">
         <f aca="false">IFERROR(B60/$B$68,"")</f>
         <v>0.132867132867133</v>
       </c>
-      <c r="G60" s="75" t="str">
+      <c r="G60" s="72" t="str">
         <f aca="false">IFERROR(SUMIFS(工单[处理天数],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;")/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;"),"-")</f>
         <v>-</v>
       </c>
-      <c r="H60" s="69" t="n">
+      <c r="H60" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>0.928571428571429</v>
       </c>
-      <c r="I60" s="76" t="n">
+      <c r="I60" s="73" t="n">
         <f aca="false">SUMIFS(工单[耗材费(元)],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A60)</f>
         <v>0</v>
       </c>
@@ -14447,38 +14442,38 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="74" t="s">
+      <c r="A62" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="B62" s="68" t="n">
+      <c r="B62" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62)</f>
         <v>15</v>
       </c>
-      <c r="C62" s="68" t="n">
+      <c r="C62" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[完成情况],"已完成")</f>
         <v>11</v>
       </c>
-      <c r="D62" s="68" t="n">
+      <c r="D62" s="64" t="n">
         <f aca="false">B62-C62</f>
         <v>4</v>
       </c>
-      <c r="E62" s="69" t="n">
+      <c r="E62" s="65" t="n">
         <f aca="false">IFERROR(C62/B62,"")</f>
         <v>0.733333333333333</v>
       </c>
-      <c r="F62" s="69" t="n">
+      <c r="F62" s="65" t="n">
         <f aca="false">IFERROR(B62/$B$68,"")</f>
         <v>0.104895104895105</v>
       </c>
-      <c r="G62" s="75" t="str">
+      <c r="G62" s="72" t="str">
         <f aca="false">IFERROR(SUMIFS(工单[处理天数],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;")/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;"),"-")</f>
         <v>-</v>
       </c>
-      <c r="H62" s="69" t="n">
+      <c r="H62" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I62" s="76" t="n">
+      <c r="I62" s="73" t="n">
         <f aca="false">SUMIFS(工单[耗材费(元)],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A62)</f>
         <v>0</v>
       </c>
@@ -14521,38 +14516,38 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="68" t="n">
+      <c r="B64" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64)</f>
         <v>4</v>
       </c>
-      <c r="C64" s="68" t="n">
+      <c r="C64" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[完成情况],"已完成")</f>
         <v>4</v>
       </c>
-      <c r="D64" s="68" t="n">
+      <c r="D64" s="64" t="n">
         <f aca="false">B64-C64</f>
         <v>0</v>
       </c>
-      <c r="E64" s="69" t="n">
+      <c r="E64" s="65" t="n">
         <f aca="false">IFERROR(C64/B64,"")</f>
         <v>1</v>
       </c>
-      <c r="F64" s="69" t="n">
+      <c r="F64" s="65" t="n">
         <f aca="false">IFERROR(B64/$B$68,"")</f>
         <v>0.027972027972028</v>
       </c>
-      <c r="G64" s="75" t="str">
+      <c r="G64" s="72" t="str">
         <f aca="false">IFERROR(SUMIFS(工单[处理天数],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;")/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;"),"-")</f>
         <v>-</v>
       </c>
-      <c r="H64" s="69" t="str">
+      <c r="H64" s="65" t="str">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64,工单[维修评价],"&lt;&gt;"),"")</f>
         <v/>
       </c>
-      <c r="I64" s="76" t="n">
+      <c r="I64" s="73" t="n">
         <f aca="false">SUMIFS(工单[耗材费(元)],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A64)</f>
         <v>0</v>
       </c>
@@ -14595,38 +14590,38 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="74" t="s">
+      <c r="A66" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="B66" s="68" t="n">
+      <c r="B66" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66)</f>
         <v>4</v>
       </c>
-      <c r="C66" s="68" t="n">
+      <c r="C66" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[完成情况],"已完成")</f>
         <v>4</v>
       </c>
-      <c r="D66" s="68" t="n">
+      <c r="D66" s="64" t="n">
         <f aca="false">B66-C66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="69" t="n">
+      <c r="E66" s="65" t="n">
         <f aca="false">IFERROR(C66/B66,"")</f>
         <v>1</v>
       </c>
-      <c r="F66" s="69" t="n">
+      <c r="F66" s="65" t="n">
         <f aca="false">IFERROR(B66/$B$68,"")</f>
         <v>0.027972027972028</v>
       </c>
-      <c r="G66" s="75" t="str">
+      <c r="G66" s="72" t="str">
         <f aca="false">IFERROR(SUMIFS(工单[处理天数],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;")/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[完成情况],"已完成",工单[完成日期],"&lt;&gt;"),"-")</f>
         <v>-</v>
       </c>
-      <c r="H66" s="69" t="n">
+      <c r="H66" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I66" s="76" t="n">
+      <c r="I66" s="73" t="n">
         <f aca="false">SUMIFS(工单[耗材费(元)],工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[维修类别],$A66)</f>
         <v>0</v>
       </c>
@@ -14782,39 +14777,39 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="74" t="str">
+      <c r="A73" s="71" t="str">
         <f aca="false">设置!E10&amp;""</f>
         <v>2栋</v>
       </c>
-      <c r="B73" s="68" t="n">
+      <c r="B73" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73)</f>
         <v>7</v>
       </c>
-      <c r="C73" s="68" t="n">
+      <c r="C73" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[类型],"入户")</f>
         <v>6</v>
       </c>
-      <c r="D73" s="68" t="n">
+      <c r="D73" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[类型],"公区")</f>
         <v>1</v>
       </c>
-      <c r="E73" s="68" t="n">
+      <c r="E73" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[完成情况],"已完成")</f>
         <v>7</v>
       </c>
-      <c r="F73" s="68" t="n">
+      <c r="F73" s="64" t="n">
         <f aca="false">B73-E73</f>
         <v>0</v>
       </c>
-      <c r="G73" s="69" t="n">
+      <c r="G73" s="65" t="n">
         <f aca="false">IFERROR(E73/B73,"")</f>
         <v>1</v>
       </c>
-      <c r="H73" s="69" t="n">
+      <c r="H73" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A73,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I73" s="68" t="n">
+      <c r="I73" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A73,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
@@ -14858,39 +14853,39 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="74" t="str">
+      <c r="A75" s="71" t="str">
         <f aca="false">设置!E12&amp;""</f>
         <v>4栋</v>
       </c>
-      <c r="B75" s="68" t="n">
+      <c r="B75" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75)</f>
         <v>6</v>
       </c>
-      <c r="C75" s="68" t="n">
+      <c r="C75" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[类型],"入户")</f>
         <v>6</v>
       </c>
-      <c r="D75" s="68" t="n">
+      <c r="D75" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[类型],"公区")</f>
         <v>0</v>
       </c>
-      <c r="E75" s="68" t="n">
+      <c r="E75" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[完成情况],"已完成")</f>
         <v>6</v>
       </c>
-      <c r="F75" s="68" t="n">
+      <c r="F75" s="64" t="n">
         <f aca="false">B75-E75</f>
         <v>0</v>
       </c>
-      <c r="G75" s="69" t="n">
+      <c r="G75" s="65" t="n">
         <f aca="false">IFERROR(E75/B75,"")</f>
         <v>1</v>
       </c>
-      <c r="H75" s="69" t="n">
+      <c r="H75" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A75,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I75" s="68" t="n">
+      <c r="I75" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A75,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
@@ -14934,39 +14929,39 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="74" t="str">
+      <c r="A77" s="71" t="str">
         <f aca="false">设置!E14&amp;""</f>
         <v>6栋</v>
       </c>
-      <c r="B77" s="68" t="n">
+      <c r="B77" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77)</f>
         <v>17</v>
       </c>
-      <c r="C77" s="68" t="n">
+      <c r="C77" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[类型],"入户")</f>
         <v>17</v>
       </c>
-      <c r="D77" s="68" t="n">
+      <c r="D77" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[类型],"公区")</f>
         <v>0</v>
       </c>
-      <c r="E77" s="68" t="n">
+      <c r="E77" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[完成情况],"已完成")</f>
         <v>13</v>
       </c>
-      <c r="F77" s="68" t="n">
+      <c r="F77" s="64" t="n">
         <f aca="false">B77-E77</f>
         <v>4</v>
       </c>
-      <c r="G77" s="69" t="n">
+      <c r="G77" s="65" t="n">
         <f aca="false">IFERROR(E77/B77,"")</f>
         <v>0.764705882352941</v>
       </c>
-      <c r="H77" s="69" t="n">
+      <c r="H77" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A77,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>0.933333333333333</v>
       </c>
-      <c r="I77" s="68" t="n">
+      <c r="I77" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A77,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
@@ -15010,39 +15005,39 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="74" t="str">
+      <c r="A79" s="71" t="str">
         <f aca="false">设置!E16&amp;""</f>
         <v>8栋</v>
       </c>
-      <c r="B79" s="68" t="n">
+      <c r="B79" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79)</f>
         <v>16</v>
       </c>
-      <c r="C79" s="68" t="n">
+      <c r="C79" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[类型],"入户")</f>
         <v>15</v>
       </c>
-      <c r="D79" s="68" t="n">
+      <c r="D79" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[类型],"公区")</f>
         <v>1</v>
       </c>
-      <c r="E79" s="68" t="n">
+      <c r="E79" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[完成情况],"已完成")</f>
         <v>14</v>
       </c>
-      <c r="F79" s="68" t="n">
+      <c r="F79" s="64" t="n">
         <f aca="false">B79-E79</f>
         <v>2</v>
       </c>
-      <c r="G79" s="69" t="n">
+      <c r="G79" s="65" t="n">
         <f aca="false">IFERROR(E79/B79,"")</f>
         <v>0.875</v>
       </c>
-      <c r="H79" s="69" t="n">
+      <c r="H79" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A79,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I79" s="68" t="n">
+      <c r="I79" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A79,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
@@ -15086,39 +15081,39 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="74" t="str">
+      <c r="A81" s="71" t="str">
         <f aca="false">设置!E18&amp;""</f>
         <v>10栋</v>
       </c>
-      <c r="B81" s="68" t="n">
+      <c r="B81" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81)</f>
         <v>16</v>
       </c>
-      <c r="C81" s="68" t="n">
+      <c r="C81" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[类型],"入户")</f>
         <v>13</v>
       </c>
-      <c r="D81" s="68" t="n">
+      <c r="D81" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[类型],"公区")</f>
         <v>3</v>
       </c>
-      <c r="E81" s="68" t="n">
+      <c r="E81" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[完成情况],"已完成")</f>
         <v>14</v>
       </c>
-      <c r="F81" s="68" t="n">
+      <c r="F81" s="64" t="n">
         <f aca="false">B81-E81</f>
         <v>2</v>
       </c>
-      <c r="G81" s="69" t="n">
+      <c r="G81" s="65" t="n">
         <f aca="false">IFERROR(E81/B81,"")</f>
         <v>0.875</v>
       </c>
-      <c r="H81" s="69" t="n">
+      <c r="H81" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A81,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I81" s="68" t="n">
+      <c r="I81" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A81,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
@@ -15162,39 +15157,39 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="74" t="str">
+      <c r="A83" s="71" t="str">
         <f aca="false">设置!E20&amp;""</f>
         <v>商铺</v>
       </c>
-      <c r="B83" s="68" t="n">
+      <c r="B83" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83)</f>
         <v>1</v>
       </c>
-      <c r="C83" s="68" t="n">
+      <c r="C83" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[类型],"入户")</f>
         <v>1</v>
       </c>
-      <c r="D83" s="68" t="n">
+      <c r="D83" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[类型],"公区")</f>
         <v>0</v>
       </c>
-      <c r="E83" s="68" t="n">
+      <c r="E83" s="64" t="n">
         <f aca="false">COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[完成情况],"已完成")</f>
         <v>1</v>
       </c>
-      <c r="F83" s="68" t="n">
+      <c r="F83" s="64" t="n">
         <f aca="false">B83-E83</f>
         <v>0</v>
       </c>
-      <c r="G83" s="69" t="n">
+      <c r="G83" s="65" t="n">
         <f aca="false">IFERROR(E83/B83,"")</f>
         <v>1</v>
       </c>
-      <c r="H83" s="69" t="n">
+      <c r="H83" s="65" t="n">
         <f aca="false">IFERROR((COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[维修评价],"非常满意")+COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[维修评价],"满意"))/COUNTIFS(工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末,工单[楼栋],$A83,工单[维修评价],"&lt;&gt;"),"")</f>
         <v>1</v>
       </c>
-      <c r="I83" s="68" t="n">
+      <c r="I83" s="64" t="n">
         <f aca="false">COUNTIFS(工单[楼栋],$A83,工单[该户第几次],2,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
@@ -15408,59 +15403,59 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="86" t="str">
+      <c r="A90" s="84" t="str">
         <f aca="false">设置!A10&amp;""</f>
         <v>李师傅</v>
       </c>
-      <c r="B90" s="87" t="n">
+      <c r="B90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],B$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],B$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="C90" s="87" t="n">
+      <c r="C90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],C$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],C$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="D90" s="87" t="n">
+      <c r="D90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],D$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],D$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>2</v>
       </c>
-      <c r="E90" s="87" t="n">
+      <c r="E90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],E$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],E$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="F90" s="87" t="n">
+      <c r="F90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],F$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],F$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>5</v>
       </c>
-      <c r="G90" s="87" t="n">
+      <c r="G90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],G$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],G$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>3</v>
       </c>
-      <c r="H90" s="87" t="n">
+      <c r="H90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],H$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],H$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>5</v>
       </c>
-      <c r="I90" s="87" t="n">
+      <c r="I90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],I$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],I$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>6</v>
       </c>
-      <c r="J90" s="87" t="n">
+      <c r="J90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],J$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],J$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>6</v>
       </c>
-      <c r="K90" s="87" t="n">
+      <c r="K90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],K$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],K$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>8</v>
       </c>
-      <c r="L90" s="87" t="n">
+      <c r="L90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],L$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],L$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>3</v>
       </c>
-      <c r="M90" s="87" t="n">
+      <c r="M90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],M$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],M$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="N90" s="87" t="n">
+      <c r="N90" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A90,工单[楼栋],N$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A90,工单[楼栋],N$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
@@ -15524,59 +15519,59 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="86" t="str">
+      <c r="A92" s="84" t="str">
         <f aca="false">设置!A12&amp;""</f>
         <v>陈师傅</v>
       </c>
-      <c r="B92" s="87" t="n">
+      <c r="B92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],B$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],B$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="C92" s="87" t="n">
+      <c r="C92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],C$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],C$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="D92" s="87" t="n">
+      <c r="D92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],D$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],D$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>3</v>
       </c>
-      <c r="E92" s="87" t="n">
+      <c r="E92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],E$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],E$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="F92" s="87" t="n">
+      <c r="F92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],F$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],F$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>2</v>
       </c>
-      <c r="G92" s="87" t="n">
+      <c r="G92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],G$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],G$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="H92" s="87" t="n">
+      <c r="H92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],H$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],H$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="I92" s="87" t="n">
+      <c r="I92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],I$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],I$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>1</v>
       </c>
-      <c r="J92" s="87" t="n">
+      <c r="J92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],J$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],J$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="K92" s="87" t="n">
+      <c r="K92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],K$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],K$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>2</v>
       </c>
-      <c r="L92" s="87" t="n">
+      <c r="L92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],L$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],L$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>3</v>
       </c>
-      <c r="M92" s="87" t="n">
+      <c r="M92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],M$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],M$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>0</v>
       </c>
-      <c r="N92" s="87" t="n">
+      <c r="N92" s="85" t="n">
         <f aca="false">COUNTIFS(工单[跟进人1],$A92,工单[楼栋],N$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)+COUNTIFS(工单[跟进人2],$A92,工单[楼栋],N$88,工单[报修日期],"&gt;="&amp;期初,工单[报修日期],"&lt;="&amp;期末)</f>
         <v>2</v>
       </c>
@@ -16040,52 +16035,52 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="n">
+      <c r="A10" s="48" t="n">
         <f aca="false">IF($O10=0,"",2)</f>
         <v>2</v>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="50" t="n">
         <f aca="false">IF($O10=0,"",INDEX(工单[报修日期],$O10-ROW(工单[#Headers])))</f>
         <v>45784</v>
       </c>
-      <c r="C10" s="54" t="str">
+      <c r="C10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[类型],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D10" s="54" t="str">
+      <c r="D10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[房号/位置],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>504</v>
       </c>
-      <c r="E10" s="55" t="str">
+      <c r="E10" s="49" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[报修问题描述],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>燃气灶点火打不着</v>
       </c>
-      <c r="F10" s="55"/>
-      <c r="G10" s="54" t="str">
+      <c r="F10" s="49"/>
+      <c r="G10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[维修类别],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>燃气厨电</v>
       </c>
-      <c r="H10" s="54" t="str">
+      <c r="H10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[跟进人1],$O10-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O10-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O10-ROW(工单[#Headers]))))</f>
         <v>张师傅</v>
       </c>
-      <c r="I10" s="54" t="str">
+      <c r="I10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[完成情况],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J10" s="57" t="str">
+      <c r="J10" s="51" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[处理天数],$O10-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K10" s="54" t="str">
+      <c r="K10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[维修评价],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L10" s="55" t="str">
+      <c r="L10" s="49" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[维修备注],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M10" s="54" t="str">
+      <c r="M10" s="48" t="str">
         <f aca="false">IF($O10=0,"",INDEX(工单[单据编号],$O10-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-504-0507-02</v>
       </c>
@@ -16150,52 +16145,52 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="n">
+      <c r="A12" s="48" t="n">
         <f aca="false">IF($O12=0,"",4)</f>
         <v>4</v>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="50" t="n">
         <f aca="false">IF($O12=0,"",INDEX(工单[报修日期],$O12-ROW(工单[#Headers])))</f>
         <v>45781</v>
       </c>
-      <c r="C12" s="54" t="str">
+      <c r="C12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[类型],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D12" s="54" t="str">
+      <c r="D12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[房号/位置],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>402</v>
       </c>
-      <c r="E12" s="55" t="str">
+      <c r="E12" s="49" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[报修问题描述],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>卫生间下水道返臭</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="54" t="str">
+      <c r="F12" s="49"/>
+      <c r="G12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[维修类别],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>给排水</v>
       </c>
-      <c r="H12" s="54" t="str">
+      <c r="H12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[跟进人1],$O12-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O12-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O12-ROW(工单[#Headers]))))</f>
         <v>张师傅</v>
       </c>
-      <c r="I12" s="54" t="str">
+      <c r="I12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[完成情况],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J12" s="57" t="str">
+      <c r="J12" s="51" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[处理天数],$O12-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K12" s="54" t="str">
+      <c r="K12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[维修评价],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L12" s="55" t="str">
+      <c r="L12" s="49" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[维修备注],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M12" s="54" t="str">
+      <c r="M12" s="48" t="str">
         <f aca="false">IF($O12=0,"",INDEX(工单[单据编号],$O12-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-402-0504</v>
       </c>
@@ -16260,52 +16255,52 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="n">
+      <c r="A14" s="48" t="n">
         <f aca="false">IF($O14=0,"",6)</f>
         <v>6</v>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="50" t="n">
         <f aca="false">IF($O14=0,"",INDEX(工单[报修日期],$O14-ROW(工单[#Headers])))</f>
         <v>45780</v>
       </c>
-      <c r="C14" s="54" t="str">
+      <c r="C14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[类型],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D14" s="54" t="str">
+      <c r="D14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[房号/位置],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>1503</v>
       </c>
-      <c r="E14" s="55" t="str">
+      <c r="E14" s="49" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[报修问题描述],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>玄关踢脚线脱落</v>
       </c>
-      <c r="F14" s="55"/>
-      <c r="G14" s="54" t="str">
+      <c r="F14" s="49"/>
+      <c r="G14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[维修类别],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>墙地饰面</v>
       </c>
-      <c r="H14" s="54" t="str">
+      <c r="H14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[跟进人1],$O14-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O14-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O14-ROW(工单[#Headers]))))</f>
         <v>张师傅</v>
       </c>
-      <c r="I14" s="54" t="str">
+      <c r="I14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[完成情况],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J14" s="57" t="str">
+      <c r="J14" s="51" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[处理天数],$O14-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K14" s="54" t="str">
+      <c r="K14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[维修评价],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L14" s="55" t="str">
+      <c r="L14" s="49" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[维修备注],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M14" s="54" t="str">
+      <c r="M14" s="48" t="str">
         <f aca="false">IF($O14=0,"",INDEX(工单[单据编号],$O14-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-1503-0503</v>
       </c>
@@ -16370,52 +16365,52 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="n">
+      <c r="A16" s="48" t="n">
         <f aca="false">IF($O16=0,"",8)</f>
         <v>8</v>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="50" t="n">
         <f aca="false">IF($O16=0,"",INDEX(工单[报修日期],$O16-ROW(工单[#Headers])))</f>
         <v>45780</v>
       </c>
-      <c r="C16" s="54" t="str">
+      <c r="C16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[类型],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D16" s="54" t="str">
+      <c r="D16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[房号/位置],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>504</v>
       </c>
-      <c r="E16" s="55" t="str">
+      <c r="E16" s="49" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[报修问题描述],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>次卧门把手松动</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="54" t="str">
+      <c r="F16" s="49"/>
+      <c r="G16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[维修类别],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>门窗五金</v>
       </c>
-      <c r="H16" s="54" t="str">
+      <c r="H16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[跟进人1],$O16-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O16-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O16-ROW(工单[#Headers]))))</f>
         <v>刘师傅</v>
       </c>
-      <c r="I16" s="54" t="str">
+      <c r="I16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[完成情况],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J16" s="57" t="str">
+      <c r="J16" s="51" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[处理天数],$O16-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K16" s="54" t="str">
+      <c r="K16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[维修评价],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L16" s="55" t="str">
+      <c r="L16" s="49" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[维修备注],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M16" s="54" t="str">
+      <c r="M16" s="48" t="str">
         <f aca="false">IF($O16=0,"",INDEX(工单[单据编号],$O16-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-504-0503</v>
       </c>
@@ -16480,52 +16475,52 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="n">
+      <c r="A18" s="48" t="n">
         <f aca="false">IF($O18=0,"",10)</f>
         <v>10</v>
       </c>
-      <c r="B18" s="56" t="n">
+      <c r="B18" s="50" t="n">
         <f aca="false">IF($O18=0,"",INDEX(工单[报修日期],$O18-ROW(工单[#Headers])))</f>
         <v>45780</v>
       </c>
-      <c r="C18" s="54" t="str">
+      <c r="C18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[类型],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D18" s="54" t="str">
+      <c r="D18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[房号/位置],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>1904</v>
       </c>
-      <c r="E18" s="55" t="str">
+      <c r="E18" s="49" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[报修问题描述],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>卫生间门关不上</v>
       </c>
-      <c r="F18" s="55"/>
-      <c r="G18" s="54" t="str">
+      <c r="F18" s="49"/>
+      <c r="G18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[维修类别],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>门窗五金</v>
       </c>
-      <c r="H18" s="54" t="str">
+      <c r="H18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[跟进人1],$O18-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O18-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O18-ROW(工单[#Headers]))))</f>
         <v>李师傅</v>
       </c>
-      <c r="I18" s="54" t="str">
+      <c r="I18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[完成情况],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J18" s="57" t="str">
+      <c r="J18" s="51" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[处理天数],$O18-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K18" s="54" t="str">
+      <c r="K18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[维修评价],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L18" s="55" t="str">
+      <c r="L18" s="49" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[维修备注],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M18" s="54" t="str">
+      <c r="M18" s="48" t="str">
         <f aca="false">IF($O18=0,"",INDEX(工单[单据编号],$O18-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-1904-0503</v>
       </c>
@@ -16590,52 +16585,52 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="54" t="n">
+      <c r="A20" s="48" t="n">
         <f aca="false">IF($O20=0,"",12)</f>
         <v>12</v>
       </c>
-      <c r="B20" s="56" t="n">
+      <c r="B20" s="50" t="n">
         <f aca="false">IF($O20=0,"",INDEX(工单[报修日期],$O20-ROW(工单[#Headers])))</f>
         <v>45779</v>
       </c>
-      <c r="C20" s="54" t="str">
+      <c r="C20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[类型],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D20" s="54" t="str">
+      <c r="D20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[房号/位置],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>201</v>
       </c>
-      <c r="E20" s="55" t="str">
+      <c r="E20" s="49" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[报修问题描述],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>房门锁舌弹不回来</v>
       </c>
-      <c r="F20" s="55"/>
-      <c r="G20" s="54" t="str">
+      <c r="F20" s="49"/>
+      <c r="G20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[维修类别],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>门窗五金</v>
       </c>
-      <c r="H20" s="54" t="str">
+      <c r="H20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[跟进人1],$O20-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O20-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O20-ROW(工单[#Headers]))))</f>
         <v>张师傅</v>
       </c>
-      <c r="I20" s="54" t="str">
+      <c r="I20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[完成情况],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J20" s="57" t="str">
+      <c r="J20" s="51" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[处理天数],$O20-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K20" s="54" t="str">
+      <c r="K20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[维修评价],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L20" s="55" t="str">
+      <c r="L20" s="49" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[维修备注],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M20" s="54" t="str">
+      <c r="M20" s="48" t="str">
         <f aca="false">IF($O20=0,"",INDEX(工单[单据编号],$O20-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-201-0502</v>
       </c>
@@ -16700,52 +16695,52 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="n">
+      <c r="A22" s="48" t="n">
         <f aca="false">IF($O22=0,"",14)</f>
         <v>14</v>
       </c>
-      <c r="B22" s="56" t="n">
+      <c r="B22" s="50" t="n">
         <f aca="false">IF($O22=0,"",INDEX(工单[报修日期],$O22-ROW(工单[#Headers])))</f>
         <v>45778</v>
       </c>
-      <c r="C22" s="54" t="str">
+      <c r="C22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[类型],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D22" s="54" t="str">
+      <c r="D22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[房号/位置],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>701</v>
       </c>
-      <c r="E22" s="55" t="str">
+      <c r="E22" s="49" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[报修问题描述],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>次卧墙面受潮鼓包起皮</v>
       </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="54" t="str">
+      <c r="F22" s="49"/>
+      <c r="G22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[维修类别],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>墙地饰面</v>
       </c>
-      <c r="H22" s="54" t="str">
+      <c r="H22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[跟进人1],$O22-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O22-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O22-ROW(工单[#Headers]))))</f>
         <v>李师傅</v>
       </c>
-      <c r="I22" s="54" t="str">
+      <c r="I22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[完成情况],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>跟进中</v>
       </c>
-      <c r="J22" s="57" t="n">
+      <c r="J22" s="51" t="n">
         <f aca="false">IF($O22=0,"",INDEX(工单[处理天数],$O22-ROW(工单[#Headers])))</f>
         <v>6</v>
       </c>
-      <c r="K22" s="54" t="str">
+      <c r="K22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[维修评价],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>非常满意</v>
       </c>
-      <c r="L22" s="55" t="str">
+      <c r="L22" s="49" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[维修备注],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>已铲除鼓包批第一遍腻子，待干透后约第二次上门</v>
       </c>
-      <c r="M22" s="54" t="str">
+      <c r="M22" s="48" t="str">
         <f aca="false">IF($O22=0,"",INDEX(工单[单据编号],$O22-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-701-0501</v>
       </c>
@@ -16810,52 +16805,52 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="n">
+      <c r="A24" s="48" t="n">
         <f aca="false">IF($O24=0,"",16)</f>
         <v>16</v>
       </c>
-      <c r="B24" s="56" t="n">
+      <c r="B24" s="50" t="n">
         <f aca="false">IF($O24=0,"",INDEX(工单[报修日期],$O24-ROW(工单[#Headers])))</f>
         <v>45778</v>
       </c>
-      <c r="C24" s="54" t="str">
+      <c r="C24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[类型],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>入户</v>
       </c>
-      <c r="D24" s="54" t="str">
+      <c r="D24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[房号/位置],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>2004</v>
       </c>
-      <c r="E24" s="55" t="str">
+      <c r="E24" s="49" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[报修问题描述],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>主卧空调出风口结露滴水</v>
       </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="54" t="str">
+      <c r="F24" s="49"/>
+      <c r="G24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[维修类别],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>空调暖通</v>
       </c>
-      <c r="H24" s="54" t="str">
+      <c r="H24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[跟进人1],$O24-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O24-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O24-ROW(工单[#Headers]))))</f>
         <v>张师傅</v>
       </c>
-      <c r="I24" s="54" t="str">
+      <c r="I24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[完成情况],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>已完成</v>
       </c>
-      <c r="J24" s="57" t="str">
+      <c r="J24" s="51" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[处理天数],$O24-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K24" s="54" t="str">
+      <c r="K24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[维修评价],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>一般</v>
       </c>
-      <c r="L24" s="55" t="str">
+      <c r="L24" s="49" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[维修备注],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>已调整出风角度并清洗滤网</v>
       </c>
-      <c r="M24" s="54" t="str">
+      <c r="M24" s="48" t="str">
         <f aca="false">IF($O24=0,"",INDEX(工单[单据编号],$O24-ROW(工单[#Headers]))&amp;"")</f>
         <v>6-2004-0501</v>
       </c>
@@ -16920,52 +16915,52 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="54" t="str">
+      <c r="A26" s="48" t="str">
         <f aca="false">IF($O26=0,"",18)</f>
         <v/>
       </c>
-      <c r="B26" s="56" t="str">
+      <c r="B26" s="50" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[报修日期],$O26-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="C26" s="54" t="str">
+      <c r="C26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[类型],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="D26" s="54" t="str">
+      <c r="D26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[房号/位置],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="E26" s="55" t="str">
+      <c r="E26" s="49" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[报修问题描述],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="F26" s="55"/>
-      <c r="G26" s="54" t="str">
+      <c r="F26" s="49"/>
+      <c r="G26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[维修类别],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="H26" s="54" t="str">
+      <c r="H26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[跟进人1],$O26-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O26-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O26-ROW(工单[#Headers]))))</f>
         <v/>
       </c>
-      <c r="I26" s="54" t="str">
+      <c r="I26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[完成情况],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="J26" s="57" t="str">
+      <c r="J26" s="51" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[处理天数],$O26-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K26" s="54" t="str">
+      <c r="K26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[维修评价],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="L26" s="55" t="str">
+      <c r="L26" s="49" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[维修备注],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M26" s="54" t="str">
+      <c r="M26" s="48" t="str">
         <f aca="false">IF($O26=0,"",INDEX(工单[单据编号],$O26-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
@@ -17030,52 +17025,52 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="54" t="str">
+      <c r="A28" s="48" t="str">
         <f aca="false">IF($O28=0,"",20)</f>
         <v/>
       </c>
-      <c r="B28" s="56" t="str">
+      <c r="B28" s="50" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[报修日期],$O28-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="C28" s="54" t="str">
+      <c r="C28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[类型],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="D28" s="54" t="str">
+      <c r="D28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[房号/位置],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="E28" s="55" t="str">
+      <c r="E28" s="49" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[报修问题描述],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="F28" s="55"/>
-      <c r="G28" s="54" t="str">
+      <c r="F28" s="49"/>
+      <c r="G28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[维修类别],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="H28" s="54" t="str">
+      <c r="H28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[跟进人1],$O28-ROW(工单[#Headers]))&amp;IF(INDEX(工单[跟进人2],$O28-ROW(工单[#Headers]))="","","、"&amp;INDEX(工单[跟进人2],$O28-ROW(工单[#Headers]))))</f>
         <v/>
       </c>
-      <c r="I28" s="54" t="str">
+      <c r="I28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[完成情况],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="J28" s="57" t="str">
+      <c r="J28" s="51" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[处理天数],$O28-ROW(工单[#Headers])))</f>
         <v/>
       </c>
-      <c r="K28" s="54" t="str">
+      <c r="K28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[维修评价],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="L28" s="55" t="str">
+      <c r="L28" s="49" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[维修备注],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>
-      <c r="M28" s="54" t="str">
+      <c r="M28" s="48" t="str">
         <f aca="false">IF($O28=0,"",INDEX(工单[单据编号],$O28-ROW(工单[#Headers]))&amp;"")</f>
         <v/>
       </c>

--- a/works/repair-ledger/repair-ledger-sample.xlsx
+++ b/works/repair-ledger/repair-ledger-sample.xlsx
@@ -3166,7 +3166,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1600" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3174,13 +3174,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1600" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>各维修类别报修量</a:t>
+              <a:t>各类别工单（已完成 / 未结）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3196,32 +3196,31 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>仪表盘!B56</c:f>
+              <c:f>仪表盘!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>报修量</c:v>
+                  <c:v>已完成</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="6a9bcc"/>
+              <a:srgbClr val="788c5d"/>
             </a:solidFill>
-            <a:ln w="9360">
+            <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="6a9bcc"/>
+                <a:srgbClr val="788c5d"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3290,7 +3289,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>仪表盘!$B$57:$B$66</c:f>
+              <c:f>仪表盘!$C$57:$C$66</c:f>
               <c:numCache>
                 <c:formatCode>0;\-0;\-</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3298,19 +3297,19 @@
                   <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>4</c:v>
@@ -3328,15 +3327,143 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:gapWidth val="60"/>
-        <c:overlap val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>仪表盘!D56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>未结</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="d97757"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="d97757"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>仪表盘!$A$57:$A$66</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>门窗五金</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>电气照明</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>给排水</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>空调暖通</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>渗漏防水</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>墙地饰面</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>燃气厨电</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>弱电门禁</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>公共设施</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>其他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>仪表盘!$D$57:$D$66</c:f>
+              <c:numCache>
+                <c:formatCode>0;\-0;\-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="50"/>
+        <c:overlap val="100"/>
         <c:axId val="39315557"/>
         <c:axId val="71068984"/>
       </c:barChart>
       <c:catAx>
         <c:axId val="39315557"/>
         <c:scaling>
-          <c:orientation val="maxMin"/>
+          <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3417,6 +3544,30 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -3446,7 +3597,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1600" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3454,7 +3605,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1600" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3912,7 +4063,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>474120</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>66</xdr:row>
       <xdr:rowOff>218160</xdr:rowOff>
     </xdr:to>
@@ -3923,7 +4074,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6625440" y="13230360"/>
-        <a:ext cx="4139640" cy="2951640"/>
+        <a:ext cx="3665520" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3942,7 +4093,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>474120</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>81</xdr:row>
       <xdr:rowOff>27360</xdr:rowOff>
     </xdr:to>
@@ -3953,7 +4104,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6625440" y="16583040"/>
-        <a:ext cx="4139640" cy="2951640"/>
+        <a:ext cx="3665520" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">

--- a/works/repair-ledger/repair-ledger-sample.xlsx
+++ b/works/repair-ledger/repair-ledger-sample.xlsx
@@ -3180,7 +3180,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>各类别工单（已完成 / 未结）</a:t>
+              <a:t>各类别工单</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3611,7 +3611,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>各楼栋工单（已完成 / 未结）</a:t>
+              <a:t>各楼栋工单</a:t>
             </a:r>
           </a:p>
         </c:rich>

--- a/works/repair-ledger/repair-ledger-sample.xlsx
+++ b/works/repair-ledger/repair-ledger-sample.xlsx
@@ -5,20 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="使用说明" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="工单台账" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="仪表盘" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="单元查询" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="设置" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="使用说明" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">仪表盘!$A$1:$N$93</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">使用说明!$A$1:$D$35</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">单元查询!$A$1:$M$29</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">工单台账!$6:$6</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">仪表盘!$A$1:$N$93</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">使用说明!$A$1:$D$35</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">单元查询!$A$1:$M$29</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">工单台账!$6:$6</definedName>
     <definedName function="false" hidden="false" name="可派单" vbProcedure="false">设置!$B$9:$B$14</definedName>
     <definedName function="false" hidden="false" name="基准日" vbProcedure="false">设置!$B$6</definedName>
     <definedName function="false" hidden="false" name="师傅" vbProcedure="false">设置!$A$9:$A$13</definedName>
